--- a/database/event/1853/event_1853_evp_summary.xlsx
+++ b/database/event/1853/event_1853_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>2.7402</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8167</v>
+        <v>2.7494</v>
       </c>
       <c r="E2" t="n">
         <v>8.0154</v>
@@ -548,7 +548,7 @@
         <v>1.9443</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8761</v>
+        <v>1.8218</v>
       </c>
       <c r="E3" t="n">
         <v>5.6871</v>
@@ -594,7 +594,7 @@
         <v>1.7367</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6308</v>
+        <v>1.5799</v>
       </c>
       <c r="E4" t="n">
         <v>5.0799</v>
@@ -640,7 +640,7 @@
         <v>1.2331</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0357</v>
+        <v>0.9931</v>
       </c>
       <c r="E5" t="n">
         <v>3.6069</v>
@@ -686,7 +686,7 @@
         <v>0.9666</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7208</v>
+        <v>0.6825</v>
       </c>
       <c r="E6" t="n">
         <v>2.8274</v>
@@ -732,7 +732,7 @@
         <v>0.9078000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6514</v>
+        <v>0.614</v>
       </c>
       <c r="E7" t="n">
         <v>2.6554</v>
@@ -778,7 +778,7 @@
         <v>0.8419</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5735</v>
+        <v>0.5372</v>
       </c>
       <c r="E8" t="n">
         <v>2.4627</v>
@@ -824,7 +824,7 @@
         <v>0.6276</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3202</v>
+        <v>0.2874</v>
       </c>
       <c r="E9" t="n">
         <v>1.8357</v>
@@ -870,7 +870,7 @@
         <v>0.6015</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2894</v>
+        <v>0.2571</v>
       </c>
       <c r="E10" t="n">
         <v>1.7595</v>
@@ -916,7 +916,7 @@
         <v>0.5339</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2095</v>
+        <v>0.1783</v>
       </c>
       <c r="E11" t="n">
         <v>1.5617</v>
@@ -962,7 +962,7 @@
         <v>0.504</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1742</v>
+        <v>0.1435</v>
       </c>
       <c r="E12" t="n">
         <v>1.4743</v>
@@ -1008,7 +1008,7 @@
         <v>0.4878</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1551</v>
+        <v>0.1246</v>
       </c>
       <c r="E13" t="n">
         <v>1.427</v>
@@ -1054,7 +1054,7 @@
         <v>0.3529</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0044</v>
+        <v>-0.0327</v>
       </c>
       <c r="E14" t="n">
         <v>1.0322</v>
@@ -1100,7 +1100,7 @@
         <v>0.3138</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0506</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="E15" t="n">
         <v>0.9179</v>
@@ -1146,7 +1146,7 @@
         <v>0.2333</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1457</v>
+        <v>-0.172</v>
       </c>
       <c r="E16" t="n">
         <v>0.6824</v>
@@ -1192,7 +1192,7 @@
         <v>0.2064</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1775</v>
+        <v>-0.2034</v>
       </c>
       <c r="E17" t="n">
         <v>0.6036</v>
@@ -1238,7 +1238,7 @@
         <v>0.0795</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3275</v>
+        <v>-0.3513</v>
       </c>
       <c r="E18" t="n">
         <v>0.2324</v>
@@ -1284,7 +1284,7 @@
         <v>0.0569</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3541</v>
+        <v>-0.3776</v>
       </c>
       <c r="E19" t="n">
         <v>0.1664</v>
@@ -1330,7 +1330,7 @@
         <v>0.0408</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3732</v>
+        <v>-0.3964</v>
       </c>
       <c r="E20" t="n">
         <v>0.1193</v>
@@ -1376,7 +1376,7 @@
         <v>0.0198</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.398</v>
+        <v>-0.4209</v>
       </c>
       <c r="E21" t="n">
         <v>0.0578</v>
@@ -1422,7 +1422,7 @@
         <v>0.0018</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4192</v>
+        <v>-0.4418</v>
       </c>
       <c r="E22" t="n">
         <v>0.0054</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0708</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5051</v>
+        <v>-0.5265</v>
       </c>
       <c r="E23" t="n">
         <v>-0.2072</v>
@@ -1514,7 +1514,7 @@
         <v>-0.0762</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5114</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-0.223</v>
@@ -1560,7 +1560,7 @@
         <v>-0.1405</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5874</v>
+        <v>-0.6077</v>
       </c>
       <c r="E25" t="n">
         <v>-0.4111</v>
@@ -1606,7 +1606,7 @@
         <v>-0.1433</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5908</v>
+        <v>-0.611</v>
       </c>
       <c r="E26" t="n">
         <v>-0.4193</v>
@@ -1652,7 +1652,7 @@
         <v>-0.1861</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6413</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>-0.5445</v>
@@ -1698,7 +1698,7 @@
         <v>-0.2181</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6791</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="E28" t="n">
         <v>-0.638</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2216</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6832</v>
+        <v>-0.7022</v>
       </c>
       <c r="E29" t="n">
         <v>-0.6482</v>
@@ -1790,7 +1790,7 @@
         <v>-0.2413</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7065</v>
+        <v>-0.7251</v>
       </c>
       <c r="E30" t="n">
         <v>-0.7059</v>
@@ -1836,7 +1836,7 @@
         <v>-0.279</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7511</v>
+        <v>-0.7691</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8162</v>
@@ -1882,7 +1882,7 @@
         <v>-0.4479</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9507</v>
+        <v>-0.9659</v>
       </c>
       <c r="E32" t="n">
         <v>-1.3102</v>
@@ -1928,7 +1928,7 @@
         <v>-0.4516</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.955</v>
+        <v>-0.9702</v>
       </c>
       <c r="E33" t="n">
         <v>-1.3209</v>
@@ -1974,7 +1974,7 @@
         <v>-0.4535</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.9724</v>
       </c>
       <c r="E34" t="n">
         <v>-1.3265</v>
@@ -2020,7 +2020,7 @@
         <v>-0.4904</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0009</v>
+        <v>-1.0154</v>
       </c>
       <c r="E35" t="n">
         <v>-1.4345</v>
@@ -2066,7 +2066,7 @@
         <v>-0.6837</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2293</v>
+        <v>-1.2407</v>
       </c>
       <c r="E36" t="n">
         <v>-2</v>
@@ -2112,7 +2112,7 @@
         <v>-0.7587</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3179</v>
+        <v>-1.3281</v>
       </c>
       <c r="E37" t="n">
         <v>-2.2193</v>
@@ -2158,7 +2158,7 @@
         <v>-0.8692</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4484</v>
+        <v>-1.4568</v>
       </c>
       <c r="E38" t="n">
         <v>-2.5424</v>
@@ -2204,7 +2204,7 @@
         <v>-1.4204</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.0998</v>
+        <v>-2.0992</v>
       </c>
       <c r="E39" t="n">
         <v>-4.1549</v>
@@ -2250,7 +2250,7 @@
         <v>-1.5316</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.2313</v>
+        <v>-2.2288</v>
       </c>
       <c r="E40" t="n">
         <v>-4.4802</v>
@@ -2296,7 +2296,7 @@
         <v>-2.4315</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.2946</v>
+        <v>-3.2775</v>
       </c>
       <c r="E41" t="n">
         <v>-7.1124</v>

--- a/database/event/1853/event_1853_evp_summary.xlsx
+++ b/database/event/1853/event_1853_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.0154</v>
+        <v>6.7532</v>
       </c>
       <c r="C2" t="n">
-        <v>2.7402</v>
+        <v>2.3087</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7494</v>
+        <v>2.4107</v>
       </c>
       <c r="E2" t="n">
-        <v>8.0154</v>
+        <v>6.7532</v>
       </c>
       <c r="F2" t="n">
-        <v>3.3632</v>
+        <v>2.9963</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6522</v>
+        <v>3.7569</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3632</v>
+        <v>5.0706</v>
       </c>
       <c r="I2" t="n">
-        <v>2.726</v>
+        <v>2.6365</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6522</v>
+        <v>3.7569</v>
       </c>
       <c r="K2" t="n">
         <v>156</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3782</v>
+        <v>6.3934</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.6871</v>
+        <v>5.9674</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9443</v>
+        <v>2.0401</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8218</v>
+        <v>2.056</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6871</v>
+        <v>5.9674</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2051</v>
+        <v>2.6395</v>
       </c>
       <c r="G3" t="n">
-        <v>3.482</v>
+        <v>3.3279</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2051</v>
+        <v>3.8136</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7873</v>
+        <v>1.9829</v>
       </c>
       <c r="J3" t="n">
-        <v>3.482</v>
+        <v>3.3279</v>
       </c>
       <c r="K3" t="n">
         <v>156</v>
@@ -575,7 +575,7 @@
         <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2693</v>
+        <v>5.3108</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0799</v>
+        <v>4.6269</v>
       </c>
       <c r="C4" t="n">
-        <v>1.7367</v>
+        <v>1.5818</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5799</v>
+        <v>1.4508</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0799</v>
+        <v>4.6269</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4306</v>
+        <v>4.1412</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6493</v>
+        <v>0.4857</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2649</v>
+        <v>9.104799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.2673</v>
+        <v>4.7341</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6493</v>
+        <v>0.4857</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>4.9166</v>
+        <v>5.219799999999999</v>
       </c>
       <c r="N4" t="n">
         <v>246</v>
@@ -630,139 +630,139 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.6069</v>
+        <v>3.0892</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2331</v>
+        <v>1.0561</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9931</v>
+        <v>0.7566000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>3.6069</v>
+        <v>3.0892</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5994</v>
+        <v>3.0892</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5994</v>
+        <v>3.4237</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9174</v>
+        <v>3.4237</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0075</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="L5" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.9249</v>
+        <v>3.4237</v>
       </c>
       <c r="N5" t="n">
-        <v>246</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8274</v>
+        <v>2.8199</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9666</v>
+        <v>0.964</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6825</v>
+        <v>0.635</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8274</v>
+        <v>2.8199</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8274</v>
+        <v>2.5992</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.2207</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8274</v>
+        <v>3.6717</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8274</v>
+        <v>1.9091</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.2207</v>
       </c>
       <c r="K6" t="n">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8274</v>
+        <v>2.1298</v>
       </c>
       <c r="N6" t="n">
-        <v>183</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6554</v>
+        <v>2.7192</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9296</v>
       </c>
       <c r="D7" t="n">
-        <v>0.614</v>
+        <v>0.5896</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6554</v>
+        <v>2.7192</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3609</v>
+        <v>3.168</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2945</v>
+        <v>-0.4488</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3609</v>
+        <v>5.6759</v>
       </c>
       <c r="I7" t="n">
-        <v>1.9136</v>
+        <v>2.9512</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2945</v>
+        <v>-0.4488</v>
       </c>
       <c r="K7" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2081</v>
+        <v>2.5024</v>
       </c>
       <c r="N7" t="n">
-        <v>304</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8">
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8419</v>
+        <v>0.8821</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5372</v>
+        <v>0.5268</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4627</v>
+        <v>2.5801</v>
       </c>
       <c r="N8" t="n">
         <v>240</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.8357</v>
+        <v>2.5462</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6276</v>
+        <v>0.8705000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2874</v>
+        <v>0.5115</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8357</v>
+        <v>2.5462</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8357</v>
+        <v>2.2823</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.2639</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8357</v>
+        <v>2.5552</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8357</v>
+        <v>1.3286</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.2639</v>
       </c>
       <c r="K9" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8357</v>
+        <v>1.5925</v>
       </c>
       <c r="N9" t="n">
-        <v>183</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.7595</v>
+        <v>2.396</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6015</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2571</v>
+        <v>0.4437</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7595</v>
+        <v>2.396</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7806</v>
+        <v>2.396</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0211</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7806</v>
+        <v>2.396</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2538</v>
+        <v>2.396</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0211</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>183</v>
       </c>
       <c r="L10" t="n">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.2327</v>
+        <v>2.396</v>
       </c>
       <c r="N10" t="n">
-        <v>246</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5617</v>
+        <v>2.2245</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5339</v>
+        <v>0.7605</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1783</v>
+        <v>0.3662</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5617</v>
+        <v>2.2245</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4112</v>
+        <v>1.6009</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1505</v>
+        <v>0.6236</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4112</v>
+        <v>1.6009</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1438</v>
+        <v>0.8324</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1505</v>
+        <v>0.6236</v>
       </c>
       <c r="K11" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2943</v>
+        <v>1.456</v>
       </c>
       <c r="N11" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.4743</v>
+        <v>2.1794</v>
       </c>
       <c r="C12" t="n">
-        <v>0.504</v>
+        <v>0.7451</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1435</v>
+        <v>0.3459</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4743</v>
+        <v>2.1794</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5515</v>
+        <v>2.9737</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9228</v>
+        <v>-0.7943</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5515</v>
+        <v>4.9912</v>
       </c>
       <c r="I12" t="n">
-        <v>0.447</v>
+        <v>2.5952</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9228</v>
+        <v>-0.7943</v>
       </c>
       <c r="K12" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3698</v>
+        <v>1.8009</v>
       </c>
       <c r="N12" t="n">
-        <v>304</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.427</v>
+        <v>2.0562</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4878</v>
+        <v>0.703</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1246</v>
+        <v>0.2903</v>
       </c>
       <c r="E13" t="n">
-        <v>1.427</v>
+        <v>2.0562</v>
       </c>
       <c r="F13" t="n">
-        <v>2.129</v>
+        <v>2.5003</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.702</v>
+        <v>-0.4441</v>
       </c>
       <c r="H13" t="n">
-        <v>2.129</v>
+        <v>3.3232</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7256</v>
+        <v>1.7279</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.702</v>
+        <v>-0.4441</v>
       </c>
       <c r="K13" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>123</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0236</v>
+        <v>1.2838</v>
       </c>
       <c r="N13" t="n">
         <v>279</v>
@@ -1044,127 +1044,127 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.0322</v>
+        <v>1.8747</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3529</v>
+        <v>0.6409</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0327</v>
+        <v>0.2083</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0322</v>
+        <v>1.8747</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0322</v>
+        <v>1.5332</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.3415</v>
       </c>
       <c r="H14" t="n">
-        <v>1.0322</v>
+        <v>1.5332</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0322</v>
+        <v>0.7972</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.3415</v>
       </c>
       <c r="K14" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0322</v>
+        <v>1.1387</v>
       </c>
       <c r="N14" t="n">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9179</v>
+        <v>1.5473</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3138</v>
+        <v>0.529</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.0605</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9179</v>
+        <v>1.5473</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9179</v>
+        <v>2.0198</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.4725</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9179</v>
+        <v>2.0198</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9179</v>
+        <v>1.0502</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.4725</v>
       </c>
       <c r="K15" t="n">
-        <v>129</v>
+        <v>226</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9179</v>
+        <v>0.5777000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6824</v>
+        <v>1.4395</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2333</v>
+        <v>0.4921</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.172</v>
+        <v>0.0118</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6824</v>
+        <v>1.4395</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4555</v>
+        <v>1.368</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2269</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4555</v>
+        <v>1.368</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3692</v>
+        <v>0.7113</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2269</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="K16" t="n">
         <v>212</v>
@@ -1173,7 +1173,7 @@
         <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5961</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>267</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2064</v>
+        <v>0.459</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2034</v>
+        <v>-0.0319</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6036</v>
+        <v>1.3425</v>
       </c>
       <c r="N17" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.2324</v>
+        <v>1.2077</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0795</v>
+        <v>0.4129</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3513</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2324</v>
+        <v>1.2077</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3484</v>
+        <v>1.2077</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.116</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3484</v>
+        <v>1.2077</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2824</v>
+        <v>1.2077</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.116</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1664</v>
+        <v>1.2077</v>
       </c>
       <c r="N18" t="n">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.1664</v>
+        <v>1.1898</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0569</v>
+        <v>0.4068</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3776</v>
+        <v>-0.1009</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1664</v>
+        <v>1.1898</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1388</v>
+        <v>1.0668</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0276</v>
+        <v>0.123</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1388</v>
+        <v>1.0668</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1125</v>
+        <v>0.5547</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0276</v>
+        <v>0.123</v>
       </c>
       <c r="K19" t="n">
         <v>226</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1401</v>
+        <v>0.6777</v>
       </c>
       <c r="N19" t="n">
         <v>304</v>
@@ -1320,170 +1320,170 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1193</v>
+        <v>0.8852</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0408</v>
+        <v>0.3026</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3964</v>
+        <v>-0.2384</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1193</v>
+        <v>0.8852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9412</v>
+        <v>0.8852</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8219</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9412</v>
+        <v>0.8852</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7629</v>
+        <v>0.8852</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8219</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>226</v>
+        <v>120</v>
       </c>
       <c r="L20" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.05899999999999994</v>
+        <v>0.8852</v>
       </c>
       <c r="N20" t="n">
-        <v>304</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0198</v>
+        <v>0.2467</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4209</v>
+        <v>-0.3122</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0578</v>
+        <v>0.7216</v>
       </c>
       <c r="N21" t="n">
-        <v>120</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0054</v>
+        <v>0.4507</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0018</v>
+        <v>0.1541</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4418</v>
+        <v>-0.4345</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0054</v>
+        <v>0.4507</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0054</v>
+        <v>0.3443</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.1064</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0054</v>
+        <v>0.3443</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0054</v>
+        <v>0.179</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.1064</v>
       </c>
       <c r="K22" t="n">
-        <v>183</v>
+        <v>212</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0054</v>
+        <v>0.2854</v>
       </c>
       <c r="N22" t="n">
-        <v>183</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0708</v>
+        <v>0.1213</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5265</v>
+        <v>-0.4779</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2072</v>
+        <v>0.3547</v>
       </c>
       <c r="N23" t="n">
         <v>183</v>
@@ -1504,47 +1504,47 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.223</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0762</v>
+        <v>0.0324</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.5953000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.223</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1527</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0703</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1527</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1238</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.0703</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>212</v>
+        <v>120</v>
       </c>
       <c r="L24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1941</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>267</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1405</v>
+        <v>-0.0132</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6077</v>
+        <v>-0.6555</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4111</v>
+        <v>-0.0387</v>
       </c>
       <c r="N25" t="n">
         <v>240</v>
@@ -1596,231 +1596,231 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.4193</v>
+        <v>-0.2327</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1433</v>
+        <v>-0.0796</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.611</v>
+        <v>-0.7431</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.4193</v>
+        <v>-0.2327</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3306</v>
+        <v>-0.2327</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9113</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.3306</v>
+        <v>-0.2327</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0785</v>
+        <v>-0.2327</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9113</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="L26" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1672</v>
+        <v>-0.2327</v>
       </c>
       <c r="N26" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1861</v>
+        <v>-0.0953</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.7639</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.5445</v>
+        <v>-0.2789</v>
       </c>
       <c r="N27" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2181</v>
+        <v>-0.1287</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6981000000000001</v>
+        <v>-0.8080000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.638</v>
+        <v>-0.3766</v>
       </c>
       <c r="N28" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2216</v>
+        <v>-0.1457</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7022</v>
+        <v>-0.8304</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6482</v>
+        <v>-0.4261</v>
       </c>
       <c r="N29" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7059</v>
+        <v>-0.5671</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2413</v>
+        <v>-0.1939</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7251</v>
+        <v>-0.894</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7059</v>
+        <v>-0.5671</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.7059</v>
+        <v>-1.4938</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.9267</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.7059</v>
+        <v>-1.4938</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7059</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.9267</v>
       </c>
       <c r="K30" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7059</v>
+        <v>0.15</v>
       </c>
       <c r="N30" t="n">
-        <v>129</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.279</v>
+        <v>-0.205</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7691</v>
+        <v>-0.9087</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8162</v>
+        <v>-0.5995</v>
       </c>
       <c r="N31" t="n">
         <v>120</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.4479</v>
+        <v>-0.2955</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9659</v>
+        <v>-1.0282</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.3102</v>
+        <v>-0.8643</v>
       </c>
       <c r="N32" t="n">
         <v>240</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.4516</v>
+        <v>-0.3081</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9702</v>
+        <v>-1.0448</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.3209</v>
+        <v>-0.9011</v>
       </c>
       <c r="N33" t="n">
         <v>120</v>
@@ -1964,93 +1964,93 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.3265</v>
+        <v>-0.9406</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.4535</v>
+        <v>-0.3216</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9724</v>
+        <v>-1.0626</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.3265</v>
+        <v>-0.9406</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1259</v>
+        <v>-0.9406</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.2006</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1259</v>
+        <v>-0.9406</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9126</v>
+        <v>-0.9406</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.2006</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="L34" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1132</v>
+        <v>-0.9406</v>
       </c>
       <c r="N34" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4904</v>
+        <v>-0.5568</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0154</v>
+        <v>-1.3733</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.4345</v>
+        <v>-1.6287</v>
       </c>
       <c r="N35" t="n">
-        <v>240</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36">
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.6837</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.2407</v>
+        <v>-1.3841</v>
       </c>
       <c r="E36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="F36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="I36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-2</v>
+        <v>-1.6526</v>
       </c>
       <c r="N36" t="n">
         <v>129</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-2.2193</v>
+        <v>-1.9002</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.7587</v>
+        <v>-0.6496</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.3281</v>
+        <v>-1.4959</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.2193</v>
+        <v>-1.9002</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.2193</v>
+        <v>-1.6742</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.226</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.2193</v>
+        <v>-1.6742</v>
       </c>
       <c r="I37" t="n">
-        <v>-2.2193</v>
+        <v>-0.8705000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.226</v>
       </c>
       <c r="K37" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M37" t="n">
-        <v>-2.2193</v>
+        <v>-1.0965</v>
       </c>
       <c r="N37" t="n">
-        <v>183</v>
+        <v>279</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.5424</v>
+        <v>-2.8876</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.8692</v>
+        <v>-0.9872</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.4568</v>
+        <v>-1.9416</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.5424</v>
+        <v>-2.8876</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2414</v>
+        <v>-1.5721</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.301</v>
+        <v>-1.3155</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2414</v>
+        <v>-1.5721</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0062</v>
+        <v>-0.8174</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.301</v>
+        <v>-1.3155</v>
       </c>
       <c r="K38" t="n">
         <v>100</v>
@@ -2185,7 +2185,7 @@
         <v>146</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.3072</v>
+        <v>-2.1329</v>
       </c>
       <c r="N38" t="n">
         <v>246</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-4.1549</v>
+        <v>-5.5331</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.4204</v>
+        <v>-1.8916</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.0992</v>
+        <v>-3.1359</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.1549</v>
+        <v>-5.5331</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.5682</v>
+        <v>-4.5331</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.5867</v>
+        <v>-1</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.5682</v>
+        <v>-4.5331</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.8921</v>
+        <v>-2.357</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.5867</v>
+        <v>-1</v>
       </c>
       <c r="K39" t="n">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="L39" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.4788</v>
+        <v>-3.357</v>
       </c>
       <c r="N39" t="n">
-        <v>246</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-4.4802</v>
+        <v>-5.7555</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.5316</v>
+        <v>-1.9676</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.2288</v>
+        <v>-3.2363</v>
       </c>
       <c r="E40" t="n">
-        <v>-4.4802</v>
+        <v>-5.7555</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.4802</v>
+        <v>-5.2324</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.5231</v>
       </c>
       <c r="H40" t="n">
-        <v>-3.4802</v>
+        <v>-5.2324</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.8208</v>
+        <v>-2.7206</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.5231</v>
       </c>
       <c r="K40" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="L40" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.8208</v>
+        <v>-3.2437</v>
       </c>
       <c r="N40" t="n">
-        <v>304</v>
+        <v>246</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-7.1124</v>
+        <v>-9.798999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>-2.4315</v>
+        <v>-3.35</v>
       </c>
       <c r="D41" t="n">
-        <v>-3.2775</v>
+        <v>-5.0618</v>
       </c>
       <c r="E41" t="n">
-        <v>-7.1124</v>
+        <v>-9.798999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.2955</v>
+        <v>-9.262700000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8169</v>
+        <v>-0.5363</v>
       </c>
       <c r="H41" t="n">
-        <v>-6.2955</v>
+        <v>-9.262700000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-5.1027</v>
+        <v>-4.8162</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8169</v>
+        <v>-0.5363</v>
       </c>
       <c r="K41" t="n">
         <v>212</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.919599999999999</v>
+        <v>-5.3525</v>
       </c>
       <c r="N41" t="n">
         <v>267</v>
@@ -2429,10 +2429,10 @@
         <v>1.82</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8043</v>
+        <v>1.5296</v>
       </c>
       <c r="J2" t="n">
-        <v>43.3032</v>
+        <v>36.7104</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6212</v>
+        <v>0.6489</v>
       </c>
       <c r="J3" t="n">
-        <v>14.9088</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4429</v>
+        <v>0.5072</v>
       </c>
       <c r="J4" t="n">
-        <v>10.6296</v>
+        <v>12.1728</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0042</v>
+        <v>0.0775</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1008</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5641</v>
+        <v>-0.4952</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.5384</v>
+        <v>-11.8848</v>
       </c>
     </row>
     <row r="7">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1344</v>
+        <v>-0.1249</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.2256</v>
+        <v>-2.9976</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3399</v>
+        <v>-0.2487</v>
       </c>
       <c r="J9" t="n">
-        <v>-8.1576</v>
+        <v>-5.9688</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4661</v>
+        <v>-0.3134</v>
       </c>
       <c r="J10" t="n">
-        <v>-11.1864</v>
+        <v>-7.5216</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.38</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8708</v>
+        <v>-0.6018</v>
       </c>
       <c r="J11" t="n">
-        <v>-20.8992</v>
+        <v>-14.4432</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.636</v>
+        <v>1.4152</v>
       </c>
       <c r="J12" t="n">
-        <v>39.264</v>
+        <v>33.9648</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7139</v>
+        <v>0.7369</v>
       </c>
       <c r="J13" t="n">
-        <v>17.1336</v>
+        <v>17.6856</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.18</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4323</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>10.3752</v>
+        <v>12.084</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4058</v>
+        <v>0.4784</v>
       </c>
       <c r="J15" t="n">
-        <v>9.7392</v>
+        <v>11.4816</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.87</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5688</v>
+        <v>-0.4995</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.6512</v>
+        <v>-11.988</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.93</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0275</v>
+        <v>-0.0544</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.66</v>
+        <v>-1.3056</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.87</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1322</v>
+        <v>-0.1269</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.1728</v>
+        <v>-3.0456</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4934</v>
+        <v>-0.3355</v>
       </c>
       <c r="J19" t="n">
-        <v>-11.8416</v>
+        <v>-8.052</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6093</v>
+        <v>-0.4102</v>
       </c>
       <c r="J20" t="n">
-        <v>-14.6232</v>
+        <v>-9.844799999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.53</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6766</v>
+        <v>-0.457</v>
       </c>
       <c r="J21" t="n">
-        <v>-16.2384</v>
+        <v>-10.968</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.76</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J22" t="n">
-        <v>46.518</v>
+        <v>37.362</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6827</v>
+        <v>0.7822</v>
       </c>
       <c r="J23" t="n">
-        <v>13.654</v>
+        <v>15.644</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2752</v>
+        <v>-0.1866</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.504</v>
+        <v>-3.732</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.98</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2752</v>
+        <v>-0.1866</v>
       </c>
       <c r="J25" t="n">
-        <v>-5.504</v>
+        <v>-3.732</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5984</v>
+        <v>-0.5285</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.968</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2069</v>
+        <v>-0.184</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.138</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.72</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3322</v>
+        <v>-0.268</v>
       </c>
       <c r="J28" t="n">
-        <v>-6.644</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.5625</v>
+        <v>-0.3881</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.25</v>
+        <v>-7.762</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.5931</v>
+        <v>-0.4066</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.862</v>
+        <v>-8.132</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6793</v>
+        <v>-0.4627</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.586</v>
+        <v>-9.254</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3335</v>
+        <v>0.9367</v>
       </c>
       <c r="J32" t="n">
-        <v>36.0045</v>
+        <v>25.2909</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>1.1326</v>
+        <v>0.806</v>
       </c>
       <c r="J33" t="n">
-        <v>30.5802</v>
+        <v>21.762</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5834</v>
+        <v>0.4747</v>
       </c>
       <c r="J34" t="n">
-        <v>15.7518</v>
+        <v>12.8169</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4272</v>
+        <v>-0.3577</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.5344</v>
+        <v>-9.6579</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1733</v>
+        <v>-1.1716</v>
       </c>
       <c r="J36" t="n">
-        <v>-31.6791</v>
+        <v>-31.6332</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2823</v>
+        <v>0.2941</v>
       </c>
       <c r="J37" t="n">
-        <v>7.6221</v>
+        <v>7.9407</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1302</v>
+        <v>0.1037</v>
       </c>
       <c r="J38" t="n">
-        <v>3.5154</v>
+        <v>2.7999</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1681</v>
+        <v>-0.1312</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.5387</v>
+        <v>-3.5424</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4742</v>
+        <v>-0.3091</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.8034</v>
+        <v>-8.345700000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.659</v>
+        <v>-0.4405</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.793</v>
+        <v>-11.8935</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3124</v>
+        <v>0.2536</v>
       </c>
       <c r="J42" t="n">
-        <v>7.4976</v>
+        <v>6.0864</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2618</v>
+        <v>0.2032</v>
       </c>
       <c r="J43" t="n">
-        <v>6.2832</v>
+        <v>4.8768</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.87</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.186</v>
+        <v>-0.1483</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.464</v>
+        <v>-3.5592</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5061</v>
+        <v>-0.3329</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.1464</v>
+        <v>-7.9896</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.8803</v>
+        <v>-0.6096</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.1272</v>
+        <v>-14.6304</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8924</v>
+        <v>0.6133999999999999</v>
       </c>
       <c r="J47" t="n">
-        <v>21.4176</v>
+        <v>14.7216</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4158</v>
+        <v>0.3482</v>
       </c>
       <c r="J48" t="n">
-        <v>9.979200000000001</v>
+        <v>8.3568</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3731</v>
+        <v>0.321</v>
       </c>
       <c r="J49" t="n">
-        <v>8.9544</v>
+        <v>7.704</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2325</v>
+        <v>-0.128</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.58</v>
+        <v>-3.072</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5435</v>
+        <v>-0.3518</v>
       </c>
       <c r="J51" t="n">
-        <v>-13.044</v>
+        <v>-8.443199999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.91</v>
       </c>
       <c r="I52" t="n">
-        <v>1.8684</v>
+        <v>1.3861</v>
       </c>
       <c r="J52" t="n">
-        <v>50.4468</v>
+        <v>37.4247</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5009</v>
+        <v>0.4415</v>
       </c>
       <c r="J53" t="n">
-        <v>13.5243</v>
+        <v>11.9205</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.161</v>
+        <v>0.2222</v>
       </c>
       <c r="J54" t="n">
-        <v>4.347</v>
+        <v>5.9994</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5214</v>
+        <v>-0.453</v>
       </c>
       <c r="J55" t="n">
-        <v>-14.0778</v>
+        <v>-12.231</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6984</v>
+        <v>-0.6419</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.8568</v>
+        <v>-17.3313</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0468</v>
+        <v>0.0037</v>
       </c>
       <c r="J57" t="n">
-        <v>1.2636</v>
+        <v>0.0999</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0222</v>
+        <v>-0.0431</v>
       </c>
       <c r="J58" t="n">
-        <v>-0.5994</v>
+        <v>-1.1637</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0998</v>
+        <v>-0.0935</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.6946</v>
+        <v>-2.5245</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.536</v>
+        <v>-0.353</v>
       </c>
       <c r="J60" t="n">
-        <v>-14.472</v>
+        <v>-9.531000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5762</v>
+        <v>-0.3812</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.5574</v>
+        <v>-10.2924</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.946</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>24.596</v>
+        <v>17.7034</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5884</v>
+        <v>0.4615</v>
       </c>
       <c r="J63" t="n">
-        <v>15.2984</v>
+        <v>11.999</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3945</v>
+        <v>0.3506</v>
       </c>
       <c r="J64" t="n">
-        <v>10.257</v>
+        <v>9.115600000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5837</v>
+        <v>-0.529</v>
       </c>
       <c r="J65" t="n">
-        <v>-15.1762</v>
+        <v>-13.754</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7575</v>
+        <v>-0.7119</v>
       </c>
       <c r="J66" t="n">
-        <v>-19.695</v>
+        <v>-18.5094</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6879</v>
+        <v>0.636</v>
       </c>
       <c r="J67" t="n">
-        <v>17.8854</v>
+        <v>16.536</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4443</v>
+        <v>0.4392</v>
       </c>
       <c r="J68" t="n">
-        <v>11.5518</v>
+        <v>11.4192</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.82</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3404</v>
+        <v>-0.2127</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.8504</v>
+        <v>-5.5302</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5101</v>
+        <v>-0.3302</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.2626</v>
+        <v>-8.5852</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6745</v>
+        <v>-0.4511</v>
       </c>
       <c r="J71" t="n">
-        <v>-17.537</v>
+        <v>-11.7286</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7872</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>22.8288</v>
+        <v>16.8519</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.666</v>
+        <v>0.5073</v>
       </c>
       <c r="J73" t="n">
-        <v>19.314</v>
+        <v>14.7117</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1947</v>
+        <v>0.1871</v>
       </c>
       <c r="J74" t="n">
-        <v>5.6463</v>
+        <v>5.4259</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.03</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1045</v>
+        <v>0.1221</v>
       </c>
       <c r="J75" t="n">
-        <v>3.0305</v>
+        <v>3.5409</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9847</v>
+        <v>-0.9594</v>
       </c>
       <c r="J76" t="n">
-        <v>-28.5563</v>
+        <v>-27.8226</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.27</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4909</v>
+        <v>0.4766</v>
       </c>
       <c r="J77" t="n">
-        <v>14.2361</v>
+        <v>13.8214</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3941</v>
+        <v>0.4017</v>
       </c>
       <c r="J78" t="n">
-        <v>11.4289</v>
+        <v>11.6493</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1424</v>
+        <v>-0.0852</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.1296</v>
+        <v>-2.4708</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.461</v>
+        <v>-0.2945</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.369</v>
+        <v>-8.5405</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.3328</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.9234</v>
+        <v>-9.651199999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5228</v>
+        <v>0.6166</v>
       </c>
       <c r="J82" t="n">
-        <v>13.07</v>
+        <v>15.415</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.267</v>
+        <v>-0.1744</v>
       </c>
       <c r="J83" t="n">
-        <v>-6.675</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.8</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3494</v>
+        <v>-0.2246</v>
       </c>
       <c r="J84" t="n">
-        <v>-8.734999999999999</v>
+        <v>-5.615</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.77</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.395</v>
+        <v>-0.2542</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.875</v>
+        <v>-6.355</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.467</v>
+        <v>-0.3027</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.675</v>
+        <v>-7.5675</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3248</v>
+        <v>1.2032</v>
       </c>
       <c r="J87" t="n">
-        <v>33.12</v>
+        <v>30.08</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4303</v>
+        <v>0.4083</v>
       </c>
       <c r="J88" t="n">
-        <v>10.7575</v>
+        <v>10.2075</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0369</v>
+        <v>0.0781</v>
       </c>
       <c r="J89" t="n">
-        <v>0.9225</v>
+        <v>1.9525</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2803</v>
+        <v>-0.2182</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.0075</v>
+        <v>-5.455</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7208</v>
       </c>
       <c r="J91" t="n">
-        <v>-19.19</v>
+        <v>-18.02</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.45</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6842</v>
+        <v>0.6</v>
       </c>
       <c r="J92" t="n">
-        <v>28.0522</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1818</v>
+        <v>0.1515</v>
       </c>
       <c r="J93" t="n">
-        <v>7.4538</v>
+        <v>6.2115</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.06950000000000001</v>
+        <v>-0.0265</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.8495</v>
+        <v>-1.0865</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2296</v>
+        <v>-0.1303</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.413600000000001</v>
+        <v>-5.3423</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2626</v>
+        <v>-0.1526</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.7666</v>
+        <v>-6.2566</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3905</v>
+        <v>0.3355</v>
       </c>
       <c r="J97" t="n">
-        <v>16.0105</v>
+        <v>13.7555</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3758</v>
+        <v>0.3206</v>
       </c>
       <c r="J98" t="n">
-        <v>15.4078</v>
+        <v>13.1446</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2405</v>
+        <v>-0.1557</v>
       </c>
       <c r="J99" t="n">
-        <v>-9.8605</v>
+        <v>-6.3837</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3246</v>
+        <v>-0.2068</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.3086</v>
+        <v>-8.4788</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.46</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5455</v>
       </c>
       <c r="J101" t="n">
-        <v>-32.7139</v>
+        <v>-22.3655</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4202</v>
+        <v>0.4777</v>
       </c>
       <c r="J102" t="n">
-        <v>12.1858</v>
+        <v>13.8533</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1773</v>
+        <v>0.1666</v>
       </c>
       <c r="J103" t="n">
-        <v>5.1417</v>
+        <v>4.8314</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0538</v>
+        <v>0.0213</v>
       </c>
       <c r="J104" t="n">
-        <v>1.5602</v>
+        <v>0.6177</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.67</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.539</v>
+        <v>-0.3524</v>
       </c>
       <c r="J105" t="n">
-        <v>-15.631</v>
+        <v>-10.2196</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6664</v>
+        <v>-0.4454</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.3256</v>
+        <v>-12.9166</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.36</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9439</v>
       </c>
       <c r="J107" t="n">
-        <v>27.6399</v>
+        <v>27.3731</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8308</v>
       </c>
       <c r="J108" t="n">
-        <v>24.3948</v>
+        <v>24.0932</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.2617</v>
+        <v>0.313</v>
       </c>
       <c r="J109" t="n">
-        <v>7.5893</v>
+        <v>9.077</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2313</v>
+        <v>0.2847</v>
       </c>
       <c r="J110" t="n">
-        <v>6.7077</v>
+        <v>8.2563</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.91</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4335</v>
+        <v>-0.3625</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.5715</v>
+        <v>-10.5125</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6755</v>
+        <v>0.8339</v>
       </c>
       <c r="J112" t="n">
-        <v>18.2385</v>
+        <v>22.5153</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.89</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1648</v>
+        <v>-0.1305</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.4496</v>
+        <v>-3.5235</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2022</v>
+        <v>-0.1517</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.4594</v>
+        <v>-4.0959</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.5941</v>
+        <v>-0.3933</v>
       </c>
       <c r="J115" t="n">
-        <v>-16.0407</v>
+        <v>-10.6191</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7437</v>
+        <v>-0.504</v>
       </c>
       <c r="J116" t="n">
-        <v>-20.0799</v>
+        <v>-13.608</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.269</v>
+        <v>1.1706</v>
       </c>
       <c r="J117" t="n">
-        <v>34.263</v>
+        <v>31.6062</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0014</v>
+        <v>0.9919</v>
       </c>
       <c r="J118" t="n">
-        <v>27.0378</v>
+        <v>26.7813</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5452</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>14.7204</v>
+        <v>15.174</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.0172</v>
+        <v>0.0509</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.4644</v>
+        <v>1.3743</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.7264</v>
+        <v>-0.6717</v>
       </c>
       <c r="J121" t="n">
-        <v>-19.6128</v>
+        <v>-18.1359</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.7352</v>
+        <v>0.6501</v>
       </c>
       <c r="J122" t="n">
-        <v>19.8504</v>
+        <v>17.5527</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2741</v>
+        <v>0.2226</v>
       </c>
       <c r="J123" t="n">
-        <v>7.4007</v>
+        <v>6.0102</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0318</v>
+        <v>0.0423</v>
       </c>
       <c r="J124" t="n">
-        <v>0.8586</v>
+        <v>1.1421</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2753</v>
+        <v>-0.162</v>
       </c>
       <c r="J125" t="n">
-        <v>-7.4331</v>
+        <v>-4.374</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4901</v>
+        <v>-0.3134</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.2327</v>
+        <v>-8.4618</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.09</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2552</v>
+        <v>0.2004</v>
       </c>
       <c r="J127" t="n">
-        <v>6.8904</v>
+        <v>5.4108</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.8539</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1057</v>
+        <v>-0.0892</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.8539</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1852</v>
+        <v>-0.1337</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.0004</v>
+        <v>-3.6099</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6515</v>
+        <v>-0.4345</v>
       </c>
       <c r="J131" t="n">
-        <v>-17.5905</v>
+        <v>-11.7315</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2964</v>
+        <v>0.328</v>
       </c>
       <c r="J132" t="n">
-        <v>8.891999999999999</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.13</v>
       </c>
       <c r="I133" t="n">
-        <v>0.2805</v>
+        <v>0.3085</v>
       </c>
       <c r="J133" t="n">
-        <v>8.414999999999999</v>
+        <v>9.255000000000001</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1109</v>
+        <v>-0.0625</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.327</v>
+        <v>-1.875</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1714</v>
+        <v>-0.0992</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.142</v>
+        <v>-2.976</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3817</v>
+        <v>-0.2381</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.451</v>
+        <v>-7.143</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.2612</v>
+        <v>1.1603</v>
       </c>
       <c r="J137" t="n">
-        <v>37.836</v>
+        <v>34.809</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.16</v>
       </c>
       <c r="I138" t="n">
-        <v>0.5782</v>
+        <v>0.525</v>
       </c>
       <c r="J138" t="n">
-        <v>17.346</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.527</v>
+        <v>-0.4818</v>
       </c>
       <c r="J139" t="n">
-        <v>-15.81</v>
+        <v>-14.454</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.7329</v>
+        <v>-0.6917</v>
       </c>
       <c r="J140" t="n">
-        <v>-21.987</v>
+        <v>-20.751</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-1.0101</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="J141" t="n">
-        <v>-30.303</v>
+        <v>-29.682</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5051</v>
+        <v>0.4572</v>
       </c>
       <c r="J142" t="n">
-        <v>18.1836</v>
+        <v>16.4592</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2591</v>
+        <v>0.2181</v>
       </c>
       <c r="J143" t="n">
-        <v>9.3276</v>
+        <v>7.8516</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.095</v>
+        <v>-0.0506</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.42</v>
+        <v>-1.8216</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.92</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1948</v>
+        <v>-0.1123</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.0128</v>
+        <v>-4.0428</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4818</v>
+        <v>-0.3083</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.3448</v>
+        <v>-11.0988</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4084</v>
+        <v>0.3328</v>
       </c>
       <c r="J147" t="n">
-        <v>14.7024</v>
+        <v>11.9808</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2561</v>
+        <v>0.1957</v>
       </c>
       <c r="J148" t="n">
-        <v>9.2196</v>
+        <v>7.0452</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1623</v>
+        <v>-0.097</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.8428</v>
+        <v>-3.492</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1998</v>
+        <v>-0.1198</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.1928</v>
+        <v>-4.3128</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.3423</v>
       </c>
       <c r="J151" t="n">
-        <v>-18.9972</v>
+        <v>-12.3228</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8711</v>
+        <v>0.8509</v>
       </c>
       <c r="J152" t="n">
-        <v>25.2619</v>
+        <v>24.6761</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6574</v>
+        <v>0.6329</v>
       </c>
       <c r="J153" t="n">
-        <v>19.0646</v>
+        <v>18.3541</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6322</v>
+        <v>0.6081</v>
       </c>
       <c r="J154" t="n">
-        <v>18.3338</v>
+        <v>17.6349</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.0198</v>
+        <v>0.0318</v>
       </c>
       <c r="J155" t="n">
-        <v>-0.5742</v>
+        <v>0.9222</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.8206</v>
+        <v>-0.7773</v>
       </c>
       <c r="J156" t="n">
-        <v>-23.7974</v>
+        <v>-22.5417</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5198</v>
+        <v>0.6125</v>
       </c>
       <c r="J157" t="n">
-        <v>15.0742</v>
+        <v>17.7625</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.078</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.5781</v>
+        <v>-2.262</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.3046</v>
+        <v>-0.1955</v>
       </c>
       <c r="J159" t="n">
-        <v>-8.833399999999999</v>
+        <v>-5.6695</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.4268</v>
+        <v>-0.2748</v>
       </c>
       <c r="J160" t="n">
-        <v>-12.3772</v>
+        <v>-7.9692</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.5504</v>
+        <v>-0.3608</v>
       </c>
       <c r="J161" t="n">
-        <v>-15.9616</v>
+        <v>-10.4632</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9093</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J162" t="n">
-        <v>24.5511</v>
+        <v>23.8032</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.6227</v>
+        <v>0.5816</v>
       </c>
       <c r="J163" t="n">
-        <v>16.8129</v>
+        <v>15.7032</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0988</v>
+        <v>-0.0604</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.6676</v>
+        <v>-1.6308</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4702</v>
+        <v>-0.4151</v>
       </c>
       <c r="J165" t="n">
-        <v>-12.6954</v>
+        <v>-11.2077</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.7044</v>
+        <v>-0.6566</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.0188</v>
+        <v>-17.7282</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3464</v>
+        <v>0.3804</v>
       </c>
       <c r="J167" t="n">
-        <v>9.3528</v>
+        <v>10.2708</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.1138</v>
+        <v>0.0902</v>
       </c>
       <c r="J168" t="n">
-        <v>3.0726</v>
+        <v>2.4354</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0297</v>
+        <v>-0.0402</v>
       </c>
       <c r="J169" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-1.0854</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2009</v>
+        <v>-0.1346</v>
       </c>
       <c r="J170" t="n">
-        <v>-5.4243</v>
+        <v>-3.6342</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7976</v>
+        <v>-0.5453</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.5352</v>
+        <v>-14.7231</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0512</v>
+        <v>0.0196</v>
       </c>
       <c r="J172" t="n">
-        <v>1.3824</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0512</v>
+        <v>0.0196</v>
       </c>
       <c r="J173" t="n">
-        <v>1.3824</v>
+        <v>0.5292</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.096</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.592</v>
+        <v>-2.1519</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2772</v>
+        <v>-0.1768</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.4844</v>
+        <v>-4.7736</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.459</v>
+        <v>-0.2959</v>
       </c>
       <c r="J176" t="n">
-        <v>-12.393</v>
+        <v>-7.9893</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9081</v>
+        <v>0.8806</v>
       </c>
       <c r="J177" t="n">
-        <v>24.5187</v>
+        <v>23.7762</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0242</v>
+        <v>0.0477</v>
       </c>
       <c r="J178" t="n">
-        <v>0.6534</v>
+        <v>1.2879</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0384</v>
+        <v>-0.0065</v>
       </c>
       <c r="J179" t="n">
-        <v>-1.0368</v>
+        <v>-0.1755</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2908</v>
+        <v>-0.2383</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.8516</v>
+        <v>-6.4341</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.91</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3845</v>
+        <v>-0.3294</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.3815</v>
+        <v>-8.893800000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2798</v>
+        <v>0.3079</v>
       </c>
       <c r="J182" t="n">
-        <v>11.192</v>
+        <v>12.316</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1381</v>
+        <v>0.1405</v>
       </c>
       <c r="J183" t="n">
-        <v>5.524</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0646</v>
+        <v>-0.0355</v>
       </c>
       <c r="J184" t="n">
-        <v>-2.584</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1721</v>
+        <v>-0.0994</v>
       </c>
       <c r="J185" t="n">
-        <v>-6.884</v>
+        <v>-3.976</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2595</v>
+        <v>-0.1554</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.38</v>
+        <v>-6.216</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9991</v>
+        <v>0.9726</v>
       </c>
       <c r="J187" t="n">
-        <v>39.964</v>
+        <v>38.904</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.28</v>
       </c>
       <c r="I188" t="n">
-        <v>0.842</v>
+        <v>0.8093</v>
       </c>
       <c r="J188" t="n">
-        <v>33.68</v>
+        <v>32.372</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6744</v>
+        <v>0.6339</v>
       </c>
       <c r="J189" t="n">
-        <v>26.976</v>
+        <v>25.356</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5773</v>
+        <v>-0.5244</v>
       </c>
       <c r="J190" t="n">
-        <v>-23.092</v>
+        <v>-20.976</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.47</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.3937</v>
+        <v>-1.4255</v>
       </c>
       <c r="J191" t="n">
-        <v>-55.748</v>
+        <v>-57.02</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.8222</v>
+        <v>0.7875</v>
       </c>
       <c r="J192" t="n">
-        <v>23.8438</v>
+        <v>22.8375</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7752</v>
+        <v>0.7377</v>
       </c>
       <c r="J193" t="n">
-        <v>22.4808</v>
+        <v>21.3933</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4952</v>
+        <v>0.4521</v>
       </c>
       <c r="J194" t="n">
-        <v>14.3608</v>
+        <v>13.1109</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2513</v>
+        <v>-0.2036</v>
       </c>
       <c r="J195" t="n">
-        <v>-7.2877</v>
+        <v>-5.9044</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.3136</v>
+        <v>-1.3322</v>
       </c>
       <c r="J196" t="n">
-        <v>-38.0944</v>
+        <v>-38.6338</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.21</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4091</v>
+        <v>0.4681</v>
       </c>
       <c r="J197" t="n">
-        <v>11.8639</v>
+        <v>13.5749</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1686</v>
+        <v>0.1692</v>
       </c>
       <c r="J198" t="n">
-        <v>4.8894</v>
+        <v>4.9068</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1202</v>
+        <v>-0.07290000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.4858</v>
+        <v>-2.1141</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.199</v>
+        <v>-0.1196</v>
       </c>
       <c r="J200" t="n">
-        <v>-5.771</v>
+        <v>-3.4684</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.501</v>
+        <v>-0.323</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.529</v>
+        <v>-9.367000000000001</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.1016</v>
+        <v>0.0494</v>
       </c>
       <c r="J202" t="n">
-        <v>2.3368</v>
+        <v>1.1362</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3251</v>
+        <v>-0.2522</v>
       </c>
       <c r="J203" t="n">
-        <v>-7.4773</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.63</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.5359</v>
+        <v>-0.3625</v>
       </c>
       <c r="J204" t="n">
-        <v>-12.3257</v>
+        <v>-8.3375</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.61</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.3812</v>
       </c>
       <c r="J205" t="n">
-        <v>-12.995</v>
+        <v>-8.7676</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6347</v>
+        <v>-0.4279</v>
       </c>
       <c r="J206" t="n">
-        <v>-14.5981</v>
+        <v>-9.841699999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.664</v>
       </c>
       <c r="J207" t="n">
-        <v>17.0292</v>
+        <v>15.272</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6949</v>
+        <v>0.6213</v>
       </c>
       <c r="J208" t="n">
-        <v>15.9827</v>
+        <v>14.2899</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2715</v>
+        <v>0.2757</v>
       </c>
       <c r="J209" t="n">
-        <v>6.2445</v>
+        <v>6.3411</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1815</v>
+        <v>0.1991</v>
       </c>
       <c r="J210" t="n">
-        <v>4.1745</v>
+        <v>4.5793</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2185</v>
+        <v>-0.1151</v>
       </c>
       <c r="J211" t="n">
-        <v>-5.0255</v>
+        <v>-2.6473</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6614</v>
+        <v>0.6167</v>
       </c>
       <c r="J212" t="n">
-        <v>18.5192</v>
+        <v>17.2676</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3594</v>
+        <v>0.3164</v>
       </c>
       <c r="J213" t="n">
-        <v>10.0632</v>
+        <v>8.8592</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1685</v>
+        <v>-0.1324</v>
       </c>
       <c r="J214" t="n">
-        <v>-4.718</v>
+        <v>-3.7072</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2766</v>
+        <v>-0.2317</v>
       </c>
       <c r="J215" t="n">
-        <v>-7.7448</v>
+        <v>-6.4876</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5423</v>
+        <v>-0.4914</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.1844</v>
+        <v>-13.7592</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.06</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1853</v>
+        <v>0.1809</v>
       </c>
       <c r="J217" t="n">
-        <v>5.1884</v>
+        <v>5.0652</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1461</v>
+        <v>0.1338</v>
       </c>
       <c r="J218" t="n">
-        <v>4.0908</v>
+        <v>3.7464</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0429</v>
+        <v>-0.0439</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.2012</v>
+        <v>-1.2292</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1312</v>
+        <v>-0.0935</v>
       </c>
       <c r="J220" t="n">
-        <v>-3.6736</v>
+        <v>-2.618</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5965</v>
+        <v>-0.3933</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.702</v>
+        <v>-11.0124</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.29</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5154</v>
+        <v>0.6091</v>
       </c>
       <c r="J222" t="n">
-        <v>14.4312</v>
+        <v>17.0548</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.17</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3481</v>
+        <v>0.3905</v>
       </c>
       <c r="J223" t="n">
-        <v>9.7468</v>
+        <v>10.934</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.1245</v>
+        <v>-0.0736</v>
       </c>
       <c r="J224" t="n">
-        <v>-3.486</v>
+        <v>-2.0608</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1838</v>
+        <v>-0.1091</v>
       </c>
       <c r="J225" t="n">
-        <v>-5.1464</v>
+        <v>-3.0548</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.55</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7025</v>
+        <v>-0.4722</v>
       </c>
       <c r="J226" t="n">
-        <v>-19.67</v>
+        <v>-13.2216</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.43</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1438</v>
+        <v>1.0836</v>
       </c>
       <c r="J227" t="n">
-        <v>32.0264</v>
+        <v>30.3408</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.29</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8388</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="J228" t="n">
-        <v>23.4864</v>
+        <v>22.764</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2091</v>
+        <v>-0.1495</v>
       </c>
       <c r="J229" t="n">
-        <v>-5.8548</v>
+        <v>-4.186</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4038</v>
+        <v>-0.3413</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.3064</v>
+        <v>-9.5564</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7433</v>
+        <v>-0.6948</v>
       </c>
       <c r="J231" t="n">
-        <v>-20.8124</v>
+        <v>-19.4544</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.96</v>
       </c>
       <c r="I232" t="n">
-        <v>0.0211</v>
+        <v>-0.02</v>
       </c>
       <c r="J232" t="n">
-        <v>0.4853</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.0905</v>
+        <v>-0.097</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.0815</v>
+        <v>-2.231</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.76</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.3245</v>
+        <v>-0.2464</v>
       </c>
       <c r="J234" t="n">
-        <v>-7.4635</v>
+        <v>-5.6672</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5605</v>
+        <v>-0.376</v>
       </c>
       <c r="J235" t="n">
-        <v>-12.8915</v>
+        <v>-8.648</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.43</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8076</v>
+        <v>-0.5531</v>
       </c>
       <c r="J236" t="n">
-        <v>-18.5748</v>
+        <v>-12.7213</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.7</v>
       </c>
       <c r="I237" t="n">
-        <v>1.5891</v>
+        <v>1.3835</v>
       </c>
       <c r="J237" t="n">
-        <v>36.5493</v>
+        <v>31.8205</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.89</v>
+        <v>0.8985</v>
       </c>
       <c r="J238" t="n">
-        <v>20.47</v>
+        <v>20.6655</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4416</v>
+        <v>0.5068</v>
       </c>
       <c r="J239" t="n">
-        <v>10.1568</v>
+        <v>11.6564</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.15</v>
       </c>
       <c r="I240" t="n">
-        <v>0.3607</v>
+        <v>0.4307</v>
       </c>
       <c r="J240" t="n">
-        <v>8.296099999999999</v>
+        <v>9.9061</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.77</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8065</v>
+        <v>-0.7585</v>
       </c>
       <c r="J241" t="n">
-        <v>-18.5495</v>
+        <v>-17.4455</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.3078</v>
+        <v>1.2012</v>
       </c>
       <c r="J242" t="n">
-        <v>30.0794</v>
+        <v>27.6276</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0445</v>
+        <v>1.0359</v>
       </c>
       <c r="J243" t="n">
-        <v>24.0235</v>
+        <v>23.8257</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.4</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9801</v>
+        <v>0.9886</v>
       </c>
       <c r="J244" t="n">
-        <v>22.5423</v>
+        <v>22.7378</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.22</v>
       </c>
       <c r="I245" t="n">
-        <v>0.524</v>
+        <v>0.5965</v>
       </c>
       <c r="J245" t="n">
-        <v>12.052</v>
+        <v>13.7195</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.9034</v>
+        <v>-0.866</v>
       </c>
       <c r="J246" t="n">
-        <v>-20.7782</v>
+        <v>-19.918</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.95</v>
       </c>
       <c r="I247" t="n">
-        <v>0.0113</v>
+        <v>-0.0273</v>
       </c>
       <c r="J247" t="n">
-        <v>0.2599</v>
+        <v>-0.6279</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.84</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1807</v>
+        <v>-0.16</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.1561</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2456</v>
+        <v>-0.2027</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.6488</v>
+        <v>-4.6621</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.52</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6892</v>
+        <v>-0.466</v>
       </c>
       <c r="J250" t="n">
-        <v>-15.8516</v>
+        <v>-10.718</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.7785</v>
+        <v>-0.5313</v>
       </c>
       <c r="J251" t="n">
-        <v>-17.9055</v>
+        <v>-12.2199</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.58</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4729</v>
+        <v>1.3044</v>
       </c>
       <c r="J252" t="n">
-        <v>60.3889</v>
+        <v>53.4804</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0283</v>
+        <v>-0.0038</v>
       </c>
       <c r="J253" t="n">
-        <v>-1.1603</v>
+        <v>-0.1558</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1366</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.6006</v>
+        <v>-4.0426</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3164</v>
+        <v>-0.266</v>
       </c>
       <c r="J255" t="n">
-        <v>-12.9724</v>
+        <v>-10.906</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.62</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.0868</v>
+        <v>-1.0737</v>
       </c>
       <c r="J256" t="n">
-        <v>-44.5588</v>
+        <v>-44.0217</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.29</v>
       </c>
       <c r="I257" t="n">
-        <v>0.533</v>
+        <v>0.631</v>
       </c>
       <c r="J257" t="n">
-        <v>21.853</v>
+        <v>25.871</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2391</v>
+        <v>0.2469</v>
       </c>
       <c r="J258" t="n">
-        <v>9.803100000000001</v>
+        <v>10.1229</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.89</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2171</v>
+        <v>-0.1372</v>
       </c>
       <c r="J259" t="n">
-        <v>-8.9011</v>
+        <v>-5.6252</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4919</v>
+        <v>-0.3179</v>
       </c>
       <c r="J260" t="n">
-        <v>-20.1679</v>
+        <v>-13.0339</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.65</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.571</v>
+        <v>-0.3747</v>
       </c>
       <c r="J261" t="n">
-        <v>-23.411</v>
+        <v>-15.3627</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.15</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3721</v>
+        <v>0.411</v>
       </c>
       <c r="J262" t="n">
-        <v>8.930400000000001</v>
+        <v>9.864000000000001</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2226</v>
+        <v>0.2157</v>
       </c>
       <c r="J263" t="n">
-        <v>5.3424</v>
+        <v>5.1768</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1903</v>
+        <v>-0.1494</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.5672</v>
+        <v>-3.5856</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.6</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.4092</v>
       </c>
       <c r="J265" t="n">
-        <v>-14.7696</v>
+        <v>-9.8208</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.48</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.7645</v>
+        <v>-0.5198</v>
       </c>
       <c r="J266" t="n">
-        <v>-18.348</v>
+        <v>-12.4752</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>1.338</v>
+        <v>1.2123</v>
       </c>
       <c r="J267" t="n">
-        <v>32.112</v>
+        <v>29.0952</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1422</v>
+        <v>0.1789</v>
       </c>
       <c r="J268" t="n">
-        <v>3.4128</v>
+        <v>4.2936</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0203</v>
       </c>
       <c r="J269" t="n">
-        <v>-1.7856</v>
+        <v>-0.4872</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1775</v>
+        <v>-0.1161</v>
       </c>
       <c r="J270" t="n">
-        <v>-4.26</v>
+        <v>-2.7864</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.89</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4666</v>
+        <v>-0.4032</v>
       </c>
       <c r="J271" t="n">
-        <v>-11.1984</v>
+        <v>-9.6768</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.32</v>
       </c>
       <c r="I272" t="n">
-        <v>0.5733</v>
+        <v>0.6865</v>
       </c>
       <c r="J272" t="n">
-        <v>16.6257</v>
+        <v>19.9085</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0435</v>
+        <v>0.0148</v>
       </c>
       <c r="J273" t="n">
-        <v>1.2615</v>
+        <v>0.4292</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.88</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.2333</v>
+        <v>-0.1474</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.7657</v>
+        <v>-4.2746</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.72</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.4773</v>
+        <v>-0.3079</v>
       </c>
       <c r="J275" t="n">
-        <v>-13.8417</v>
+        <v>-8.9291</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5178</v>
+        <v>-0.3365</v>
       </c>
       <c r="J276" t="n">
-        <v>-15.0162</v>
+        <v>-9.7585</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7763</v>
+        <v>0.7386</v>
       </c>
       <c r="J277" t="n">
-        <v>22.5127</v>
+        <v>21.4194</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2868</v>
+        <v>0.2535</v>
       </c>
       <c r="J278" t="n">
-        <v>8.3172</v>
+        <v>7.3515</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0283</v>
+        <v>-0.0038</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.8207</v>
+        <v>-0.1102</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2839</v>
+        <v>-0.235</v>
       </c>
       <c r="J280" t="n">
-        <v>-8.2331</v>
+        <v>-6.815</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.5476</v>
+        <v>-0.495</v>
       </c>
       <c r="J281" t="n">
-        <v>-15.8804</v>
+        <v>-14.355</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>0.8023</v>
+        <v>1.0044</v>
       </c>
       <c r="J282" t="n">
-        <v>20.8598</v>
+        <v>26.1144</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.91</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1339</v>
+        <v>-0.1098</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.4814</v>
+        <v>-2.8548</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.8</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3424</v>
+        <v>-0.2224</v>
       </c>
       <c r="J284" t="n">
-        <v>-8.9024</v>
+        <v>-5.7824</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5173</v>
+        <v>-0.3384</v>
       </c>
       <c r="J285" t="n">
-        <v>-13.4498</v>
+        <v>-8.798400000000001</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.44</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8163</v>
+        <v>-0.5597</v>
       </c>
       <c r="J286" t="n">
-        <v>-21.2238</v>
+        <v>-14.5522</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2632</v>
+        <v>1.1653</v>
       </c>
       <c r="J287" t="n">
-        <v>32.8432</v>
+        <v>30.2978</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0373</v>
+        <v>1.0168</v>
       </c>
       <c r="J288" t="n">
-        <v>26.9698</v>
+        <v>26.4368</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.15</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4109</v>
+        <v>0.4448</v>
       </c>
       <c r="J289" t="n">
-        <v>10.6834</v>
+        <v>11.5648</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.4349</v>
+        <v>-0.3635</v>
       </c>
       <c r="J290" t="n">
-        <v>-11.3074</v>
+        <v>-9.451000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.6127</v>
       </c>
       <c r="J291" t="n">
-        <v>-17.4434</v>
+        <v>-15.9302</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.13</v>
       </c>
       <c r="I292" t="n">
-        <v>0.3994</v>
+        <v>0.4544</v>
       </c>
       <c r="J292" t="n">
-        <v>9.186199999999999</v>
+        <v>10.4512</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.7</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.4121</v>
+        <v>-0.2974</v>
       </c>
       <c r="J293" t="n">
-        <v>-9.478300000000001</v>
+        <v>-6.8402</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.5904</v>
+        <v>-0.3986</v>
       </c>
       <c r="J294" t="n">
-        <v>-13.5792</v>
+        <v>-9.1678</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.6045</v>
+        <v>-0.4079</v>
       </c>
       <c r="J295" t="n">
-        <v>-13.9035</v>
+        <v>-9.3817</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.5</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.712</v>
+        <v>-0.4828</v>
       </c>
       <c r="J296" t="n">
-        <v>-16.376</v>
+        <v>-11.1044</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.4076</v>
+        <v>1.2627</v>
       </c>
       <c r="J297" t="n">
-        <v>32.3748</v>
+        <v>29.0421</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.59</v>
       </c>
       <c r="I298" t="n">
-        <v>1.3885</v>
+        <v>1.2502</v>
       </c>
       <c r="J298" t="n">
-        <v>31.9355</v>
+        <v>28.7546</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.1105</v>
+        <v>1.0726</v>
       </c>
       <c r="J299" t="n">
-        <v>25.5415</v>
+        <v>24.6698</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.482</v>
+        <v>-0.4084</v>
       </c>
       <c r="J300" t="n">
-        <v>-11.086</v>
+        <v>-9.3932</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.2469</v>
+        <v>-1.2573</v>
       </c>
       <c r="J301" t="n">
-        <v>-28.6787</v>
+        <v>-28.9179</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0052</v>
+        <v>-0.0395</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.1144</v>
+        <v>-0.869</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2068</v>
+        <v>-0.1817</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.5496</v>
+        <v>-3.9974</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.67</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.4391</v>
+        <v>-0.3207</v>
       </c>
       <c r="J304" t="n">
-        <v>-9.6602</v>
+        <v>-7.0554</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.64</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.4996</v>
+        <v>-0.3471</v>
       </c>
       <c r="J305" t="n">
-        <v>-10.9912</v>
+        <v>-7.6362</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.29</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.9638</v>
+        <v>-0.6748</v>
       </c>
       <c r="J306" t="n">
-        <v>-21.2036</v>
+        <v>-14.8456</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.65</v>
       </c>
       <c r="I307" t="n">
-        <v>1.4447</v>
+        <v>1.2945</v>
       </c>
       <c r="J307" t="n">
-        <v>31.7834</v>
+        <v>28.479</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.49</v>
       </c>
       <c r="I308" t="n">
-        <v>1.1316</v>
+        <v>1.1001</v>
       </c>
       <c r="J308" t="n">
-        <v>24.8952</v>
+        <v>24.2022</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.7817</v>
+        <v>0.8534</v>
       </c>
       <c r="J309" t="n">
-        <v>17.1974</v>
+        <v>18.7748</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.28</v>
       </c>
       <c r="I310" t="n">
-        <v>0.6303</v>
+        <v>0.7215</v>
       </c>
       <c r="J310" t="n">
-        <v>13.8666</v>
+        <v>15.873</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3368</v>
+        <v>-0.251</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.4096</v>
+        <v>-5.522</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.23</v>
       </c>
       <c r="I312" t="n">
-        <v>0.4769</v>
+        <v>0.5535</v>
       </c>
       <c r="J312" t="n">
-        <v>12.3994</v>
+        <v>14.391</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.8</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.3407</v>
+        <v>-0.2219</v>
       </c>
       <c r="J313" t="n">
-        <v>-8.8582</v>
+        <v>-5.7694</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.8</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.3407</v>
+        <v>-0.2219</v>
       </c>
       <c r="J314" t="n">
-        <v>-8.8582</v>
+        <v>-5.7694</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.75</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.4173</v>
+        <v>-0.2708</v>
       </c>
       <c r="J315" t="n">
-        <v>-10.8498</v>
+        <v>-7.0408</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.4607</v>
+        <v>-0.2998</v>
       </c>
       <c r="J316" t="n">
-        <v>-11.9782</v>
+        <v>-7.7948</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.64</v>
       </c>
       <c r="I317" t="n">
-        <v>1.4947</v>
+        <v>1.3194</v>
       </c>
       <c r="J317" t="n">
-        <v>38.8622</v>
+        <v>34.3044</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.33</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8635</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="J318" t="n">
-        <v>22.451</v>
+        <v>22.4484</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.6724</v>
+        <v>0.6784</v>
       </c>
       <c r="J319" t="n">
-        <v>17.4824</v>
+        <v>17.6384</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4372</v>
+        <v>0.4885</v>
       </c>
       <c r="J320" t="n">
-        <v>11.3672</v>
+        <v>12.701</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-1.1835</v>
+        <v>-1.1838</v>
       </c>
       <c r="J321" t="n">
-        <v>-30.771</v>
+        <v>-30.7788</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1853/event_1853_evp_summary.xlsx
+++ b/database/event/1853/event_1853_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7532</v>
+        <v>6.8635</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3087</v>
+        <v>2.3464</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4107</v>
+        <v>2.5002</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7532</v>
+        <v>6.8635</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9963</v>
+        <v>2.8932</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7569</v>
+        <v>3.9703</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0706</v>
+        <v>4.6516</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6365</v>
+        <v>2.5118</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7569</v>
+        <v>3.9703</v>
       </c>
       <c r="K2" t="n">
         <v>156</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3934</v>
+        <v>6.4821</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9674</v>
+        <v>5.9828</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0401</v>
+        <v>2.0453</v>
       </c>
       <c r="D3" t="n">
-        <v>2.056</v>
+        <v>2.0993</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9674</v>
+        <v>5.9828</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6395</v>
+        <v>2.5519</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3279</v>
+        <v>3.4309</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8136</v>
+        <v>3.5254</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9829</v>
+        <v>1.9037</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3279</v>
+        <v>3.4309</v>
       </c>
       <c r="K3" t="n">
         <v>156</v>
@@ -575,7 +575,7 @@
         <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3108</v>
+        <v>5.3346</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6269</v>
+        <v>4.5913</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5818</v>
+        <v>1.5696</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4508</v>
+        <v>1.4659</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6269</v>
+        <v>4.5913</v>
       </c>
       <c r="F4" t="n">
-        <v>4.1412</v>
+        <v>4.0525</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4857</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>9.104799999999999</v>
+        <v>8.4764</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7341</v>
+        <v>4.5772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4857</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>5.219799999999999</v>
+        <v>5.116000000000001</v>
       </c>
       <c r="N4" t="n">
         <v>246</v>
@@ -630,231 +630,231 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.0892</v>
+        <v>2.8064</v>
       </c>
       <c r="C5" t="n">
-        <v>1.0561</v>
+        <v>0.9594</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.6533</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0892</v>
+        <v>2.8064</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0892</v>
+        <v>3.0915</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.2851</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4237</v>
+        <v>5.3058</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4237</v>
+        <v>2.8651</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-0.2851</v>
       </c>
       <c r="K5" t="n">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4237</v>
+        <v>2.58</v>
       </c>
       <c r="N5" t="n">
-        <v>183</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.8199</v>
+        <v>2.732</v>
       </c>
       <c r="C6" t="n">
-        <v>0.964</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>0.635</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8199</v>
+        <v>2.732</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5992</v>
+        <v>2.732</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2207</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6717</v>
+        <v>3.2546</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9091</v>
+        <v>3.2546</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2207</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="L6" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.1298</v>
+        <v>3.2546</v>
       </c>
       <c r="N6" t="n">
-        <v>304</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7192</v>
+        <v>2.6939</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9296</v>
+        <v>0.921</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5896</v>
+        <v>0.6021</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7192</v>
+        <v>2.6939</v>
       </c>
       <c r="F7" t="n">
-        <v>3.168</v>
+        <v>2.4763</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4488</v>
+        <v>0.2176</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6759</v>
+        <v>3.2762</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9512</v>
+        <v>1.7691</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4488</v>
+        <v>0.2176</v>
       </c>
       <c r="K7" t="n">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="L7" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5024</v>
+        <v>1.9867</v>
       </c>
       <c r="N7" t="n">
-        <v>246</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5801</v>
+        <v>2.442</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8821</v>
+        <v>0.8348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5268</v>
+        <v>0.4874</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5801</v>
+        <v>2.442</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5801</v>
+        <v>2.1428</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.2992</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5801</v>
+        <v>2.1756</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5801</v>
+        <v>1.1748</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.2992</v>
       </c>
       <c r="K8" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5801</v>
+        <v>1.474</v>
       </c>
       <c r="N8" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.5462</v>
+        <v>2.4024</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8705000000000001</v>
+        <v>0.8213</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5115</v>
+        <v>0.4694</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5462</v>
+        <v>2.4024</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2823</v>
+        <v>2.4024</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2639</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5552</v>
+        <v>2.5331</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3286</v>
+        <v>2.5331</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2639</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="L9" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5925</v>
+        <v>2.5331</v>
       </c>
       <c r="N9" t="n">
-        <v>267</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8191000000000001</v>
+        <v>0.7681</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4437</v>
+        <v>0.3986</v>
       </c>
       <c r="E10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="F10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="I10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.396</v>
+        <v>2.2469</v>
       </c>
       <c r="N10" t="n">
         <v>183</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2245</v>
+        <v>2.173</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7605</v>
+        <v>0.7429</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3662</v>
+        <v>0.365</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2245</v>
+        <v>2.173</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6009</v>
+        <v>1.4806</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6236</v>
+        <v>0.6924</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6009</v>
+        <v>1.4806</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8324</v>
+        <v>0.7995</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6236</v>
+        <v>0.6924</v>
       </c>
       <c r="K11" t="n">
         <v>226</v>
@@ -943,7 +943,7 @@
         <v>78</v>
       </c>
       <c r="M11" t="n">
-        <v>1.456</v>
+        <v>1.4919</v>
       </c>
       <c r="N11" t="n">
         <v>304</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.1794</v>
+        <v>2.0783</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7451</v>
+        <v>0.7105</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3459</v>
+        <v>0.3219</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1794</v>
+        <v>2.0783</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9737</v>
+        <v>2.8896</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7943</v>
+        <v>-0.8113</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9912</v>
+        <v>4.6397</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5952</v>
+        <v>2.5054</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7943</v>
+        <v>-0.8113</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8009</v>
+        <v>1.6941</v>
       </c>
       <c r="N12" t="n">
         <v>246</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0562</v>
+        <v>2.0349</v>
       </c>
       <c r="C13" t="n">
-        <v>0.703</v>
+        <v>0.6957</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2903</v>
+        <v>0.3021</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0562</v>
+        <v>2.0349</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5003</v>
+        <v>2.4112</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4441</v>
+        <v>-0.3763</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3232</v>
+        <v>3.0613</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7279</v>
+        <v>1.6531</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.4441</v>
+        <v>-0.3763</v>
       </c>
       <c r="K13" t="n">
         <v>156</v>
@@ -1035,7 +1035,7 @@
         <v>123</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2838</v>
+        <v>1.2768</v>
       </c>
       <c r="N13" t="n">
         <v>279</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8747</v>
+        <v>1.5716</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6409</v>
+        <v>0.5373</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2083</v>
+        <v>0.0912</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8747</v>
+        <v>1.5716</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5332</v>
+        <v>1.1735</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3415</v>
+        <v>0.3981</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5332</v>
+        <v>1.1735</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7972</v>
+        <v>0.6337</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3415</v>
+        <v>0.3981</v>
       </c>
       <c r="K14" t="n">
         <v>212</v>
@@ -1081,7 +1081,7 @@
         <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1387</v>
+        <v>1.0318</v>
       </c>
       <c r="N14" t="n">
         <v>267</v>
@@ -1090,124 +1090,124 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.5473</v>
+        <v>1.256</v>
       </c>
       <c r="C15" t="n">
-        <v>0.529</v>
+        <v>0.4294</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0605</v>
+        <v>-0.0524</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5473</v>
+        <v>1.256</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0198</v>
+        <v>1.256</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4725</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0198</v>
+        <v>1.256</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0502</v>
+        <v>1.256</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4725</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>226</v>
+        <v>129</v>
       </c>
       <c r="L15" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.5777000000000001</v>
+        <v>1.256</v>
       </c>
       <c r="N15" t="n">
-        <v>304</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4395</v>
+        <v>1.2553</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4921</v>
+        <v>0.4291</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0118</v>
+        <v>-0.0528</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4395</v>
+        <v>1.2553</v>
       </c>
       <c r="F16" t="n">
-        <v>1.368</v>
+        <v>1.7356</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.4803</v>
       </c>
       <c r="H16" t="n">
-        <v>1.368</v>
+        <v>1.7356</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7113</v>
+        <v>0.9372</v>
       </c>
       <c r="J16" t="n">
-        <v>0.07149999999999999</v>
+        <v>-0.4803</v>
       </c>
       <c r="K16" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.4569</v>
       </c>
       <c r="N16" t="n">
-        <v>267</v>
+        <v>304</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="C17" t="n">
-        <v>0.459</v>
+        <v>0.3979</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0319</v>
+        <v>-0.0944</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3425</v>
+        <v>1.1638</v>
       </c>
       <c r="N17" t="n">
         <v>129</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2077</v>
+        <v>1.161</v>
       </c>
       <c r="C18" t="n">
-        <v>0.4129</v>
+        <v>0.3969</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2077</v>
+        <v>1.161</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2077</v>
+        <v>1.0659</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.0951</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2077</v>
+        <v>1.0659</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2077</v>
+        <v>0.5756</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.0951</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2077</v>
+        <v>0.6707</v>
       </c>
       <c r="N18" t="n">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1898</v>
+        <v>0.9096</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4068</v>
+        <v>0.311</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1009</v>
+        <v>-0.2101</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1898</v>
+        <v>0.9096</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0668</v>
+        <v>0.8156</v>
       </c>
       <c r="G19" t="n">
-        <v>0.123</v>
+        <v>0.094</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0668</v>
+        <v>0.8156</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5547</v>
+        <v>0.4404</v>
       </c>
       <c r="J19" t="n">
-        <v>0.123</v>
+        <v>0.094</v>
       </c>
       <c r="K19" t="n">
         <v>226</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6777</v>
+        <v>0.5344</v>
       </c>
       <c r="N19" t="n">
         <v>304</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3026</v>
+        <v>0.2783</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2384</v>
+        <v>-0.2537</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8852</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>120</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2467</v>
+        <v>0.2181</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3122</v>
+        <v>-0.3338</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7216</v>
+        <v>0.6379</v>
       </c>
       <c r="N21" t="n">
         <v>183</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4507</v>
+        <v>0.3216</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1541</v>
+        <v>0.1099</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4345</v>
+        <v>-0.4778</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4507</v>
+        <v>0.3216</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3443</v>
+        <v>0.1839</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1064</v>
+        <v>0.1377</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3443</v>
+        <v>0.1839</v>
       </c>
       <c r="I22" t="n">
-        <v>0.179</v>
+        <v>0.0993</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1064</v>
+        <v>0.1377</v>
       </c>
       <c r="K22" t="n">
         <v>212</v>
@@ -1449,7 +1449,7 @@
         <v>55</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2854</v>
+        <v>0.237</v>
       </c>
       <c r="N22" t="n">
         <v>267</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1213</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4779</v>
+        <v>-0.4955</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3547</v>
+        <v>0.2828</v>
       </c>
       <c r="N23" t="n">
         <v>183</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0324</v>
+        <v>0.0224</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5944</v>
       </c>
       <c r="E24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="F24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.0654</v>
       </c>
       <c r="N24" t="n">
         <v>120</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0132</v>
+        <v>-0.0538</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6555</v>
+        <v>-0.6958</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0387</v>
+        <v>-0.1573</v>
       </c>
       <c r="N25" t="n">
         <v>240</v>
@@ -1596,231 +1596,231 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0796</v>
+        <v>-0.1023</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7431</v>
+        <v>-0.7605</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2327</v>
+        <v>-0.2993</v>
       </c>
       <c r="N26" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.2789</v>
+        <v>-0.3277</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0953</v>
+        <v>-0.112</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7639</v>
+        <v>-0.7734</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.2789</v>
+        <v>-0.3277</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2789</v>
+        <v>-1.3393</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.0116</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2789</v>
+        <v>-1.3393</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2789</v>
+        <v>-0.7232</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.0116</v>
       </c>
       <c r="K27" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.2789</v>
+        <v>0.2884000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>129</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1287</v>
+        <v>-0.1173</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.8080000000000001</v>
+        <v>-0.7803</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3766</v>
+        <v>-0.343</v>
       </c>
       <c r="N28" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Zeus</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="C29" t="n">
         <v>-0.1457</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8304</v>
+        <v>-0.8183</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4261</v>
+        <v>-0.4263</v>
       </c>
       <c r="N29" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Zeus</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.5671</v>
+        <v>-0.4582</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1939</v>
+        <v>-0.1566</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.894</v>
+        <v>-0.8328</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.5671</v>
+        <v>-0.4582</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4938</v>
+        <v>-0.4582</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9267</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4938</v>
+        <v>-0.4582</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7766999999999999</v>
+        <v>-0.4582</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9267</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="L30" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.15</v>
+        <v>-0.4582</v>
       </c>
       <c r="N30" t="n">
-        <v>279</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.205</v>
+        <v>-0.2152</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9087</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5995</v>
+        <v>-0.6296</v>
       </c>
       <c r="N31" t="n">
         <v>120</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2955</v>
+        <v>-0.2958</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0282</v>
+        <v>-1.0181</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8643</v>
+        <v>-0.8653</v>
       </c>
       <c r="N32" t="n">
         <v>240</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3081</v>
+        <v>-0.3189</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0448</v>
+        <v>-1.0489</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9011</v>
+        <v>-0.9329</v>
       </c>
       <c r="N33" t="n">
         <v>120</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3216</v>
+        <v>-0.335</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0626</v>
+        <v>-1.0702</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9406</v>
+        <v>-0.9798</v>
       </c>
       <c r="N34" t="n">
         <v>240</v>
@@ -2010,139 +2010,139 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>TaZ</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.6287</v>
+        <v>-1.4439</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.5568</v>
+        <v>-0.4936</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.3733</v>
+        <v>-1.2815</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.6287</v>
+        <v>-1.4439</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.6287</v>
+        <v>-1.4187</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-0.0252</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.6287</v>
+        <v>-1.4187</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.6287</v>
+        <v>-0.7661</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-0.0252</v>
       </c>
       <c r="K35" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.6287</v>
+        <v>-0.7913</v>
       </c>
       <c r="N35" t="n">
-        <v>183</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.524</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.3841</v>
+        <v>-1.3219</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>129</v>
+        <v>183</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6526</v>
+        <v>-1.5326</v>
       </c>
       <c r="N36" t="n">
-        <v>129</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TaZ</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.9002</v>
+        <v>-1.7067</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.6496</v>
+        <v>-0.5835</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.4959</v>
+        <v>-1.4011</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.9002</v>
+        <v>-1.7067</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.6742</v>
+        <v>-1.7067</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.226</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6742</v>
+        <v>-1.7067</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8705000000000001</v>
+        <v>-1.7067</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.226</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="L37" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0965</v>
+        <v>-1.7067</v>
       </c>
       <c r="N37" t="n">
-        <v>279</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.8876</v>
+        <v>-2.6419</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9872</v>
+        <v>-0.9032</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.9416</v>
+        <v>-1.8269</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.8876</v>
+        <v>-2.6419</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5721</v>
+        <v>-1.4026</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.3155</v>
+        <v>-1.2393</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5721</v>
+        <v>-1.4026</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8174</v>
+        <v>-0.7574</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.3155</v>
+        <v>-1.2393</v>
       </c>
       <c r="K38" t="n">
         <v>100</v>
@@ -2185,7 +2185,7 @@
         <v>146</v>
       </c>
       <c r="M38" t="n">
-        <v>-2.1329</v>
+        <v>-1.9967</v>
       </c>
       <c r="N38" t="n">
         <v>246</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-5.5331</v>
+        <v>-5.1236</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.8916</v>
+        <v>-1.7516</v>
       </c>
       <c r="D39" t="n">
-        <v>-3.1359</v>
+        <v>-2.9566</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.5331</v>
+        <v>-5.1236</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.5331</v>
+        <v>-4.6399</v>
       </c>
       <c r="G39" t="n">
-        <v>-1</v>
+        <v>-0.4837</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.5331</v>
+        <v>-4.6399</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.357</v>
+        <v>-2.5055</v>
       </c>
       <c r="J39" t="n">
-        <v>-1</v>
+        <v>-0.4837</v>
       </c>
       <c r="K39" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="L39" t="n">
-        <v>78</v>
+        <v>146</v>
       </c>
       <c r="M39" t="n">
-        <v>-3.357</v>
+        <v>-2.9892</v>
       </c>
       <c r="N39" t="n">
-        <v>304</v>
+        <v>246</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.7555</v>
+        <v>-5.143</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.9676</v>
+        <v>-1.7582</v>
       </c>
       <c r="D40" t="n">
-        <v>-3.2363</v>
+        <v>-2.9654</v>
       </c>
       <c r="E40" t="n">
-        <v>-5.7555</v>
+        <v>-5.143</v>
       </c>
       <c r="F40" t="n">
-        <v>-5.2324</v>
+        <v>-4.143</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.5231</v>
+        <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-5.2324</v>
+        <v>-4.143</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.7206</v>
+        <v>-2.2372</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5231</v>
+        <v>-1</v>
       </c>
       <c r="K40" t="n">
-        <v>100</v>
+        <v>226</v>
       </c>
       <c r="L40" t="n">
-        <v>146</v>
+        <v>78</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.2437</v>
+        <v>-3.2372</v>
       </c>
       <c r="N40" t="n">
-        <v>246</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-9.798999999999999</v>
+        <v>-9.0519</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.35</v>
+        <v>-3.0946</v>
       </c>
       <c r="D41" t="n">
-        <v>-5.0618</v>
+        <v>-4.7448</v>
       </c>
       <c r="E41" t="n">
-        <v>-9.798999999999999</v>
+        <v>-9.0519</v>
       </c>
       <c r="F41" t="n">
-        <v>-9.262700000000001</v>
+        <v>-8.4961</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5363</v>
+        <v>-0.5558</v>
       </c>
       <c r="H41" t="n">
-        <v>-9.262700000000001</v>
+        <v>-8.4961</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.8162</v>
+        <v>-4.5878</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5363</v>
+        <v>-0.5558</v>
       </c>
       <c r="K41" t="n">
         <v>212</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.3525</v>
+        <v>-5.143599999999999</v>
       </c>
       <c r="N41" t="n">
         <v>267</v>
@@ -2429,10 +2429,10 @@
         <v>1.82</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5296</v>
+        <v>1.6567</v>
       </c>
       <c r="J2" t="n">
-        <v>36.7104</v>
+        <v>39.7608</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6489</v>
+        <v>0.626</v>
       </c>
       <c r="J3" t="n">
-        <v>15.5736</v>
+        <v>15.024</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5072</v>
+        <v>0.4984</v>
       </c>
       <c r="J4" t="n">
-        <v>12.1728</v>
+        <v>11.9616</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0775</v>
+        <v>0.0993</v>
       </c>
       <c r="J5" t="n">
-        <v>1.86</v>
+        <v>2.3832</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4952</v>
+        <v>-0.4625</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.8848</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2557</v>
+        <v>0.239</v>
       </c>
       <c r="J7" t="n">
-        <v>6.1368</v>
+        <v>5.736</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1249</v>
+        <v>-0.1453</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9976</v>
+        <v>-3.4872</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2487</v>
+        <v>-0.2683</v>
       </c>
       <c r="J9" t="n">
-        <v>-5.9688</v>
+        <v>-6.4392</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3134</v>
+        <v>-0.3316</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.5216</v>
+        <v>-7.9584</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.38</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6018</v>
+        <v>-0.6038</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.4432</v>
+        <v>-14.4912</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4152</v>
+        <v>1.5271</v>
       </c>
       <c r="J12" t="n">
-        <v>33.9648</v>
+        <v>36.6504</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7369</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>17.6856</v>
+        <v>16.9224</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.18</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.4959</v>
       </c>
       <c r="J14" t="n">
-        <v>12.084</v>
+        <v>11.9016</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4784</v>
+        <v>0.4732</v>
       </c>
       <c r="J15" t="n">
-        <v>11.4816</v>
+        <v>11.3568</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.87</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4995</v>
+        <v>-0.4655</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.988</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.93</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0544</v>
+        <v>-0.0762</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3056</v>
+        <v>-1.8288</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.87</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1269</v>
+        <v>-0.1494</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.0456</v>
+        <v>-3.5856</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3355</v>
+        <v>-0.3541</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.052</v>
+        <v>-8.4984</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4102</v>
+        <v>-0.4253</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.844799999999999</v>
+        <v>-10.2072</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.53</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.457</v>
+        <v>-0.4695</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.968</v>
+        <v>-11.268</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.76</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J22" t="n">
-        <v>37.362</v>
+        <v>36.906</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7822</v>
+        <v>0.7498</v>
       </c>
       <c r="J23" t="n">
-        <v>15.644</v>
+        <v>14.996</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1866</v>
+        <v>-0.1643</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.732</v>
+        <v>-3.286</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.98</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1866</v>
+        <v>-0.1643</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.732</v>
+        <v>-3.286</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5285</v>
+        <v>-0.486</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.57</v>
+        <v>-9.720000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.184</v>
+        <v>-0.2098</v>
       </c>
       <c r="J27" t="n">
-        <v>-3.68</v>
+        <v>-4.196</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.72</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.268</v>
+        <v>-0.2911</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.36</v>
+        <v>-5.822</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3881</v>
+        <v>-0.4066</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.762</v>
+        <v>-8.132</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4066</v>
+        <v>-0.4241</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.132</v>
+        <v>-8.481999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4627</v>
+        <v>-0.4769</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.254</v>
+        <v>-9.538</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9367</v>
+        <v>1.0275</v>
       </c>
       <c r="J32" t="n">
-        <v>25.2909</v>
+        <v>27.7425</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>0.806</v>
+        <v>0.8874</v>
       </c>
       <c r="J33" t="n">
-        <v>21.762</v>
+        <v>23.9598</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4747</v>
+        <v>0.5238</v>
       </c>
       <c r="J34" t="n">
-        <v>12.8169</v>
+        <v>14.1426</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3577</v>
+        <v>-0.3416</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.6579</v>
+        <v>-9.2232</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1716</v>
+        <v>-1.0607</v>
       </c>
       <c r="J36" t="n">
-        <v>-31.6332</v>
+        <v>-28.6389</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2941</v>
+        <v>0.2874</v>
       </c>
       <c r="J37" t="n">
-        <v>7.9407</v>
+        <v>7.7598</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1037</v>
+        <v>0.1006</v>
       </c>
       <c r="J38" t="n">
-        <v>2.7999</v>
+        <v>2.7162</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1312</v>
+        <v>-0.1475</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.5424</v>
+        <v>-3.9825</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3091</v>
+        <v>-0.3246</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.345700000000001</v>
+        <v>-8.764200000000001</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4405</v>
+        <v>-0.4506</v>
       </c>
       <c r="J41" t="n">
-        <v>-11.8935</v>
+        <v>-12.1662</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2536</v>
+        <v>0.2502</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0864</v>
+        <v>6.0048</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2032</v>
+        <v>0.2011</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8768</v>
+        <v>4.8264</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.87</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1483</v>
+        <v>-0.166</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.5592</v>
+        <v>-3.984</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3329</v>
+        <v>-0.3486</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.9896</v>
+        <v>-8.366400000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6096</v>
+        <v>-0.6101</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.6304</v>
+        <v>-14.6424</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6133999999999999</v>
+        <v>0.7015</v>
       </c>
       <c r="J47" t="n">
-        <v>14.7216</v>
+        <v>16.836</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3482</v>
+        <v>0.3729</v>
       </c>
       <c r="J48" t="n">
-        <v>8.3568</v>
+        <v>8.9496</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.321</v>
+        <v>0.3379</v>
       </c>
       <c r="J49" t="n">
-        <v>7.704</v>
+        <v>8.1096</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.128</v>
+        <v>-0.1363</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.072</v>
+        <v>-3.2712</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3518</v>
+        <v>-0.3599</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.443199999999999</v>
+        <v>-8.637600000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.91</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3861</v>
+        <v>1.5022</v>
       </c>
       <c r="J52" t="n">
-        <v>37.4247</v>
+        <v>40.5594</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4415</v>
+        <v>0.4874</v>
       </c>
       <c r="J53" t="n">
-        <v>11.9205</v>
+        <v>13.1598</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2222</v>
+        <v>0.2337</v>
       </c>
       <c r="J54" t="n">
-        <v>5.9994</v>
+        <v>6.3099</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.453</v>
+        <v>-0.427</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.231</v>
+        <v>-11.529</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6419</v>
+        <v>-0.5971</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.3313</v>
+        <v>-16.1217</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0999</v>
+        <v>-0.2106</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0431</v>
+        <v>-0.0571</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.1637</v>
+        <v>-1.5417</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.0935</v>
+        <v>-0.1097</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.5245</v>
+        <v>-2.9619</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.353</v>
+        <v>-0.3676</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.531000000000001</v>
+        <v>-9.9252</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3812</v>
+        <v>-0.3947</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.2924</v>
+        <v>-10.6569</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.7469</v>
       </c>
       <c r="J62" t="n">
-        <v>17.7034</v>
+        <v>19.4194</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4615</v>
+        <v>0.5046</v>
       </c>
       <c r="J63" t="n">
-        <v>11.999</v>
+        <v>13.1196</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3506</v>
+        <v>0.3578</v>
       </c>
       <c r="J64" t="n">
-        <v>9.115600000000001</v>
+        <v>9.3028</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.529</v>
+        <v>-0.5026</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.754</v>
+        <v>-13.0676</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7119</v>
+        <v>-0.6652</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.5094</v>
+        <v>-17.2952</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>0.636</v>
+        <v>0.7058</v>
       </c>
       <c r="J67" t="n">
-        <v>16.536</v>
+        <v>18.3508</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4392</v>
+        <v>0.4827</v>
       </c>
       <c r="J68" t="n">
-        <v>11.4192</v>
+        <v>12.5502</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.82</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2127</v>
+        <v>-0.2276</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.5302</v>
+        <v>-5.9176</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3302</v>
+        <v>-0.3429</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.5852</v>
+        <v>-8.9154</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4511</v>
+        <v>-0.459</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.7286</v>
+        <v>-11.934</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5810999999999999</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>16.8519</v>
+        <v>18.4904</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5073</v>
+        <v>0.5558</v>
       </c>
       <c r="J73" t="n">
-        <v>14.7117</v>
+        <v>16.1182</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1871</v>
+        <v>0.1934</v>
       </c>
       <c r="J74" t="n">
-        <v>5.4259</v>
+        <v>5.6086</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.03</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1221</v>
+        <v>0.1301</v>
       </c>
       <c r="J75" t="n">
-        <v>3.5409</v>
+        <v>3.7729</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9594</v>
+        <v>-0.8813</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.8226</v>
+        <v>-25.5577</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.27</v>
       </c>
       <c r="I77" t="n">
-        <v>0.4766</v>
+        <v>0.5268</v>
       </c>
       <c r="J77" t="n">
-        <v>13.8214</v>
+        <v>15.2772</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4017</v>
+        <v>0.438</v>
       </c>
       <c r="J78" t="n">
-        <v>11.6493</v>
+        <v>12.702</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0852</v>
+        <v>-0.0968</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.4708</v>
+        <v>-2.8072</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.2945</v>
+        <v>-0.3077</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.5405</v>
+        <v>-8.923299999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.3328</v>
+        <v>-0.345</v>
       </c>
       <c r="J81" t="n">
-        <v>-9.651199999999999</v>
+        <v>-10.005</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.6166</v>
+        <v>0.5879</v>
       </c>
       <c r="J82" t="n">
-        <v>15.415</v>
+        <v>14.6975</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1744</v>
+        <v>-0.191</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.36</v>
+        <v>-4.775</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.8</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2246</v>
+        <v>-0.2412</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.615</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.77</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2542</v>
+        <v>-0.2704</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.355</v>
+        <v>-6.76</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3027</v>
+        <v>-0.3178</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.5675</v>
+        <v>-7.945</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.2032</v>
+        <v>1.1637</v>
       </c>
       <c r="J87" t="n">
-        <v>30.08</v>
+        <v>29.0925</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4083</v>
+        <v>0.4018</v>
       </c>
       <c r="J88" t="n">
-        <v>10.2075</v>
+        <v>10.045</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0781</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="J89" t="n">
-        <v>1.9525</v>
+        <v>2.2225</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2182</v>
+        <v>-0.2148</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.455</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7208</v>
+        <v>-0.6715</v>
       </c>
       <c r="J91" t="n">
-        <v>-18.02</v>
+        <v>-16.7875</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.45</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6</v>
+        <v>0.5978</v>
       </c>
       <c r="J92" t="n">
-        <v>24.6</v>
+        <v>24.5098</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1515</v>
+        <v>0.1659</v>
       </c>
       <c r="J93" t="n">
-        <v>6.2115</v>
+        <v>6.8019</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0265</v>
+        <v>-0.0298</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.0865</v>
+        <v>-1.2218</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1303</v>
+        <v>-0.141</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.3423</v>
+        <v>-5.781</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1526</v>
+        <v>-0.1639</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.2566</v>
+        <v>-6.7199</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3355</v>
+        <v>0.3339</v>
       </c>
       <c r="J97" t="n">
-        <v>13.7555</v>
+        <v>13.6899</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3206</v>
+        <v>0.3197</v>
       </c>
       <c r="J98" t="n">
-        <v>13.1446</v>
+        <v>13.1077</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1557</v>
+        <v>-0.1715</v>
       </c>
       <c r="J99" t="n">
-        <v>-6.3837</v>
+        <v>-7.0315</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2068</v>
+        <v>-0.2231</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.4788</v>
+        <v>-9.1471</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.46</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5455</v>
+        <v>-0.549</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.3655</v>
+        <v>-22.509</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4777</v>
+        <v>0.4624</v>
       </c>
       <c r="J102" t="n">
-        <v>13.8533</v>
+        <v>13.4096</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1666</v>
+        <v>0.1677</v>
       </c>
       <c r="J103" t="n">
-        <v>4.8314</v>
+        <v>4.8633</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0213</v>
+        <v>0.0153</v>
       </c>
       <c r="J104" t="n">
-        <v>0.6177</v>
+        <v>0.4437</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.67</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3524</v>
+        <v>-0.3655</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.2196</v>
+        <v>-10.5995</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4454</v>
+        <v>-0.4545</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.9166</v>
+        <v>-13.1805</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.36</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9439</v>
+        <v>0.8837</v>
       </c>
       <c r="J107" t="n">
-        <v>27.3731</v>
+        <v>25.6273</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8308</v>
+        <v>0.7831</v>
       </c>
       <c r="J108" t="n">
-        <v>24.0932</v>
+        <v>22.7099</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.313</v>
+        <v>0.3175</v>
       </c>
       <c r="J109" t="n">
-        <v>9.077</v>
+        <v>9.2075</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2847</v>
+        <v>0.2912</v>
       </c>
       <c r="J110" t="n">
-        <v>8.2563</v>
+        <v>8.444800000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.91</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3625</v>
+        <v>-0.3449</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.5125</v>
+        <v>-10.0021</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8339</v>
+        <v>0.7802</v>
       </c>
       <c r="J112" t="n">
-        <v>22.5153</v>
+        <v>21.0654</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.89</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1305</v>
+        <v>-0.1469</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.5235</v>
+        <v>-3.9663</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1517</v>
+        <v>-0.1686</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.0959</v>
+        <v>-4.5522</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3933</v>
+        <v>-0.4058</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.6191</v>
+        <v>-10.9566</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.504</v>
+        <v>-0.5107</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.608</v>
+        <v>-13.7889</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1706</v>
+        <v>1.1348</v>
       </c>
       <c r="J117" t="n">
-        <v>31.6062</v>
+        <v>30.6396</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9919</v>
+        <v>0.9337</v>
       </c>
       <c r="J118" t="n">
-        <v>26.7813</v>
+        <v>25.2099</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5464</v>
       </c>
       <c r="J119" t="n">
-        <v>15.174</v>
+        <v>14.7528</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0509</v>
+        <v>0.0701</v>
       </c>
       <c r="J120" t="n">
-        <v>1.3743</v>
+        <v>1.8927</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6717</v>
+        <v>-0.623</v>
       </c>
       <c r="J121" t="n">
-        <v>-18.1359</v>
+        <v>-16.821</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6501</v>
+        <v>0.6437</v>
       </c>
       <c r="J122" t="n">
-        <v>17.5527</v>
+        <v>17.3799</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2226</v>
+        <v>0.2367</v>
       </c>
       <c r="J123" t="n">
-        <v>6.0102</v>
+        <v>6.3909</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0423</v>
+        <v>0.0511</v>
       </c>
       <c r="J124" t="n">
-        <v>1.1421</v>
+        <v>1.3797</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.162</v>
+        <v>-0.1738</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.374</v>
+        <v>-4.6926</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3134</v>
+        <v>-0.3243</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.4618</v>
+        <v>-8.7561</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.09</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2004</v>
+        <v>0.2029</v>
       </c>
       <c r="J127" t="n">
-        <v>5.4108</v>
+        <v>5.4783</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.4084</v>
+        <v>-2.7891</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0892</v>
+        <v>-0.1033</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.4084</v>
+        <v>-2.7891</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1337</v>
+        <v>-0.1494</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.6099</v>
+        <v>-4.0338</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4345</v>
+        <v>-0.4444</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.7315</v>
+        <v>-11.9988</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.328</v>
+        <v>0.3297</v>
       </c>
       <c r="J132" t="n">
-        <v>9.84</v>
+        <v>9.891</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.13</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3085</v>
+        <v>0.3112</v>
       </c>
       <c r="J133" t="n">
-        <v>9.255000000000001</v>
+        <v>9.336</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0625</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.875</v>
+        <v>-2.157</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0992</v>
+        <v>-0.1109</v>
       </c>
       <c r="J135" t="n">
-        <v>-2.976</v>
+        <v>-3.327</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2381</v>
+        <v>-0.2517</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.143</v>
+        <v>-7.551</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1603</v>
+        <v>1.1112</v>
       </c>
       <c r="J137" t="n">
-        <v>34.809</v>
+        <v>33.336</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.16</v>
       </c>
       <c r="I138" t="n">
-        <v>0.525</v>
+        <v>0.4998</v>
       </c>
       <c r="J138" t="n">
-        <v>15.75</v>
+        <v>14.994</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4818</v>
+        <v>-0.4642</v>
       </c>
       <c r="J139" t="n">
-        <v>-14.454</v>
+        <v>-13.926</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.6917</v>
+        <v>-0.651</v>
       </c>
       <c r="J140" t="n">
-        <v>-20.751</v>
+        <v>-19.53</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.9102</v>
       </c>
       <c r="J141" t="n">
-        <v>-29.682</v>
+        <v>-27.306</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4572</v>
+        <v>0.4542</v>
       </c>
       <c r="J142" t="n">
-        <v>16.4592</v>
+        <v>16.3512</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.2181</v>
+        <v>0.227</v>
       </c>
       <c r="J143" t="n">
-        <v>7.8516</v>
+        <v>8.172000000000001</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0506</v>
+        <v>-0.0586</v>
       </c>
       <c r="J144" t="n">
-        <v>-1.8216</v>
+        <v>-2.1096</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.92</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1123</v>
+        <v>-0.1241</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.0428</v>
+        <v>-4.4676</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3083</v>
+        <v>-0.3204</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.0988</v>
+        <v>-11.5344</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3328</v>
+        <v>0.3405</v>
       </c>
       <c r="J147" t="n">
-        <v>11.9808</v>
+        <v>12.258</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1957</v>
+        <v>0.2065</v>
       </c>
       <c r="J148" t="n">
-        <v>7.0452</v>
+        <v>7.434</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.097</v>
+        <v>-0.1092</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.492</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1198</v>
+        <v>-0.1329</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.3128</v>
+        <v>-4.7844</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3423</v>
+        <v>-0.3542</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3228</v>
+        <v>-12.7512</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.8509</v>
+        <v>0.7971</v>
       </c>
       <c r="J152" t="n">
-        <v>24.6761</v>
+        <v>23.1159</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6329</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>18.3541</v>
+        <v>17.5537</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.6081</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>17.6349</v>
+        <v>16.9128</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0318</v>
+        <v>0.044</v>
       </c>
       <c r="J155" t="n">
-        <v>0.9222</v>
+        <v>1.276</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7773</v>
+        <v>-0.7201</v>
       </c>
       <c r="J156" t="n">
-        <v>-22.5417</v>
+        <v>-20.8829</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6125</v>
+        <v>0.5849</v>
       </c>
       <c r="J157" t="n">
-        <v>17.7625</v>
+        <v>16.9621</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.078</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.262</v>
+        <v>-2.6477</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1955</v>
+        <v>-0.212</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.6695</v>
+        <v>-6.148</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2748</v>
+        <v>-0.2904</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.9692</v>
+        <v>-8.4216</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3608</v>
+        <v>-0.3738</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.4632</v>
+        <v>-10.8402</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8186</v>
       </c>
       <c r="J162" t="n">
-        <v>23.8032</v>
+        <v>22.1022</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5816</v>
+        <v>0.5548</v>
       </c>
       <c r="J163" t="n">
-        <v>15.7032</v>
+        <v>14.9796</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0604</v>
+        <v>-0.0634</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.6308</v>
+        <v>-1.7118</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4151</v>
+        <v>-0.4005</v>
       </c>
       <c r="J165" t="n">
-        <v>-11.2077</v>
+        <v>-10.8135</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6566</v>
+        <v>-0.6171</v>
       </c>
       <c r="J166" t="n">
-        <v>-17.7282</v>
+        <v>-16.6617</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3804</v>
+        <v>0.3721</v>
       </c>
       <c r="J167" t="n">
-        <v>10.2708</v>
+        <v>10.0467</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0902</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J168" t="n">
-        <v>2.4354</v>
+        <v>2.4516</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0402</v>
+        <v>-0.0508</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.0854</v>
+        <v>-1.3716</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1346</v>
+        <v>-0.15</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.6342</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5453</v>
+        <v>-0.5488</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.7231</v>
+        <v>-14.8176</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0196</v>
+        <v>0.0141</v>
       </c>
       <c r="J172" t="n">
-        <v>0.5292</v>
+        <v>0.3807</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0196</v>
+        <v>0.0141</v>
       </c>
       <c r="J173" t="n">
-        <v>0.5292</v>
+        <v>0.3807</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0926</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.1519</v>
+        <v>-2.5002</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1768</v>
+        <v>-0.1928</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.7736</v>
+        <v>-5.2056</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2959</v>
+        <v>-0.3107</v>
       </c>
       <c r="J176" t="n">
-        <v>-7.9893</v>
+        <v>-8.3889</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8806</v>
+        <v>0.8179</v>
       </c>
       <c r="J177" t="n">
-        <v>23.7762</v>
+        <v>22.0833</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0477</v>
+        <v>0.0549</v>
       </c>
       <c r="J178" t="n">
-        <v>1.2879</v>
+        <v>1.4823</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0065</v>
+        <v>-0.0044</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.1755</v>
+        <v>-0.1188</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2383</v>
+        <v>-0.2368</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.4341</v>
+        <v>-6.3936</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.91</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3294</v>
+        <v>-0.3219</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.893800000000001</v>
+        <v>-8.6913</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3079</v>
+        <v>0.3108</v>
       </c>
       <c r="J182" t="n">
-        <v>12.316</v>
+        <v>12.432</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1405</v>
+        <v>0.1488</v>
       </c>
       <c r="J183" t="n">
-        <v>5.62</v>
+        <v>5.952</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0355</v>
+        <v>-0.0423</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.42</v>
+        <v>-1.692</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0994</v>
+        <v>-0.111</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.976</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1554</v>
+        <v>-0.1688</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.216</v>
+        <v>-6.752</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9726</v>
+        <v>0.9026999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>38.904</v>
+        <v>36.108</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.28</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8093</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="J188" t="n">
-        <v>32.372</v>
+        <v>30.22</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6339</v>
+        <v>0.6012</v>
       </c>
       <c r="J189" t="n">
-        <v>25.356</v>
+        <v>24.048</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5244</v>
+        <v>-0.4994</v>
       </c>
       <c r="J190" t="n">
-        <v>-20.976</v>
+        <v>-19.976</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.47</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.4255</v>
+        <v>-1.2801</v>
       </c>
       <c r="J191" t="n">
-        <v>-57.02</v>
+        <v>-51.204</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7875</v>
+        <v>0.7359</v>
       </c>
       <c r="J192" t="n">
-        <v>22.8375</v>
+        <v>21.3411</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7377</v>
+        <v>0.6923</v>
       </c>
       <c r="J193" t="n">
-        <v>21.3933</v>
+        <v>20.0767</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4521</v>
+        <v>0.438</v>
       </c>
       <c r="J194" t="n">
-        <v>13.1109</v>
+        <v>12.702</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2036</v>
+        <v>-0.2046</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.9044</v>
+        <v>-5.9334</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.3322</v>
+        <v>-1.2013</v>
       </c>
       <c r="J196" t="n">
-        <v>-38.6338</v>
+        <v>-34.8377</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.21</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4681</v>
+        <v>0.4588</v>
       </c>
       <c r="J197" t="n">
-        <v>13.5749</v>
+        <v>13.3052</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1692</v>
+        <v>0.1755</v>
       </c>
       <c r="J198" t="n">
-        <v>4.9068</v>
+        <v>5.0895</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.07290000000000001</v>
+        <v>-0.0838</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.1141</v>
+        <v>-2.4302</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1196</v>
+        <v>-0.1328</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.4684</v>
+        <v>-3.8512</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.323</v>
+        <v>-0.3355</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.367000000000001</v>
+        <v>-9.7295</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0494</v>
+        <v>0.0246</v>
       </c>
       <c r="J202" t="n">
-        <v>1.1362</v>
+        <v>0.5658</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2522</v>
+        <v>-0.273</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.8006</v>
+        <v>-6.279</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.63</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3625</v>
+        <v>-0.3801</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.3375</v>
+        <v>-8.7423</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.61</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3812</v>
+        <v>-0.3979</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.7676</v>
+        <v>-9.1517</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4279</v>
+        <v>-0.4423</v>
       </c>
       <c r="J206" t="n">
-        <v>-9.841699999999999</v>
+        <v>-10.1729</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>0.664</v>
+        <v>0.665</v>
       </c>
       <c r="J207" t="n">
-        <v>15.272</v>
+        <v>15.295</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6213</v>
+        <v>0.6252</v>
       </c>
       <c r="J208" t="n">
-        <v>14.2899</v>
+        <v>14.3796</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2757</v>
+        <v>0.2947</v>
       </c>
       <c r="J209" t="n">
-        <v>6.3411</v>
+        <v>6.7781</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.1991</v>
+        <v>0.2191</v>
       </c>
       <c r="J210" t="n">
-        <v>4.5793</v>
+        <v>5.0393</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1151</v>
+        <v>-0.1201</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.6473</v>
+        <v>-2.7623</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6167</v>
+        <v>0.5843</v>
       </c>
       <c r="J212" t="n">
-        <v>17.2676</v>
+        <v>16.3604</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3164</v>
+        <v>0.3128</v>
       </c>
       <c r="J213" t="n">
-        <v>8.8592</v>
+        <v>8.7584</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.1324</v>
+        <v>-0.137</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.7072</v>
+        <v>-3.836</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2317</v>
+        <v>-0.2323</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.4876</v>
+        <v>-6.5044</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4914</v>
+        <v>-0.471</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.7592</v>
+        <v>-13.188</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.06</v>
       </c>
       <c r="I217" t="n">
-        <v>0.1809</v>
+        <v>0.184</v>
       </c>
       <c r="J217" t="n">
-        <v>5.0652</v>
+        <v>5.152</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1338</v>
+        <v>0.1374</v>
       </c>
       <c r="J218" t="n">
-        <v>3.7464</v>
+        <v>3.8472</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0439</v>
+        <v>-0.0535</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.2292</v>
+        <v>-1.498</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.0935</v>
+        <v>-0.1065</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.618</v>
+        <v>-2.982</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3933</v>
+        <v>-0.4042</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.0124</v>
+        <v>-11.3176</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.29</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6091</v>
+        <v>0.5885</v>
       </c>
       <c r="J222" t="n">
-        <v>17.0548</v>
+        <v>16.478</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.17</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3905</v>
+        <v>0.3873</v>
       </c>
       <c r="J223" t="n">
-        <v>10.934</v>
+        <v>10.8444</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0736</v>
+        <v>-0.0843</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.0608</v>
+        <v>-2.3604</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1091</v>
+        <v>-0.1217</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.0548</v>
+        <v>-3.4076</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.55</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4722</v>
+        <v>-0.4786</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.2216</v>
+        <v>-13.4008</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.43</v>
       </c>
       <c r="I227" t="n">
-        <v>1.0836</v>
+        <v>1.0334</v>
       </c>
       <c r="J227" t="n">
-        <v>30.3408</v>
+        <v>28.9352</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.29</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7623</v>
       </c>
       <c r="J228" t="n">
-        <v>22.764</v>
+        <v>21.3444</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1495</v>
+        <v>-0.1489</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.186</v>
+        <v>-4.1692</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3413</v>
+        <v>-0.3301</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.5564</v>
+        <v>-9.242800000000001</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6948</v>
+        <v>-0.6486</v>
       </c>
       <c r="J231" t="n">
-        <v>-19.4544</v>
+        <v>-18.1608</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.96</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.02</v>
+        <v>-0.0389</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.46</v>
+        <v>-0.8947000000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.097</v>
+        <v>-0.1182</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.231</v>
+        <v>-2.7186</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.76</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2464</v>
+        <v>-0.2665</v>
       </c>
       <c r="J234" t="n">
-        <v>-5.6672</v>
+        <v>-6.1295</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.376</v>
+        <v>-0.3923</v>
       </c>
       <c r="J235" t="n">
-        <v>-8.648</v>
+        <v>-9.0229</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.43</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5531</v>
+        <v>-0.5589</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.7213</v>
+        <v>-12.8547</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.7</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3835</v>
+        <v>1.3632</v>
       </c>
       <c r="J237" t="n">
-        <v>31.8205</v>
+        <v>31.3536</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8985</v>
+        <v>0.8465</v>
       </c>
       <c r="J238" t="n">
-        <v>20.6655</v>
+        <v>19.4695</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.5068</v>
+        <v>0.4981</v>
       </c>
       <c r="J239" t="n">
-        <v>11.6564</v>
+        <v>11.4563</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.15</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4307</v>
+        <v>0.4292</v>
       </c>
       <c r="J240" t="n">
-        <v>9.9061</v>
+        <v>9.871600000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.77</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.7585</v>
+        <v>-0.698</v>
       </c>
       <c r="J241" t="n">
-        <v>-17.4455</v>
+        <v>-16.054</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2012</v>
+        <v>1.1712</v>
       </c>
       <c r="J242" t="n">
-        <v>27.6276</v>
+        <v>26.9376</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0359</v>
+        <v>0.987</v>
       </c>
       <c r="J243" t="n">
-        <v>23.8257</v>
+        <v>22.701</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.4</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9886</v>
+        <v>0.9345</v>
       </c>
       <c r="J244" t="n">
-        <v>22.7378</v>
+        <v>21.4935</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.22</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5965</v>
+        <v>0.5804</v>
       </c>
       <c r="J245" t="n">
-        <v>13.7195</v>
+        <v>13.3492</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.866</v>
+        <v>-0.7913</v>
       </c>
       <c r="J246" t="n">
-        <v>-19.918</v>
+        <v>-18.1999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.95</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0273</v>
+        <v>-0.0483</v>
       </c>
       <c r="J247" t="n">
-        <v>-0.6279</v>
+        <v>-1.1109</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.84</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.16</v>
+        <v>-0.1823</v>
       </c>
       <c r="J248" t="n">
-        <v>-3.68</v>
+        <v>-4.1929</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2027</v>
+        <v>-0.2244</v>
       </c>
       <c r="J249" t="n">
-        <v>-4.6621</v>
+        <v>-5.1612</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.52</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.466</v>
+        <v>-0.478</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.718</v>
+        <v>-10.994</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5313</v>
+        <v>-0.5391</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.2199</v>
+        <v>-12.3993</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.58</v>
       </c>
       <c r="I252" t="n">
-        <v>1.3044</v>
+        <v>1.2674</v>
       </c>
       <c r="J252" t="n">
-        <v>53.4804</v>
+        <v>51.9634</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0038</v>
+        <v>-0.0026</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.1558</v>
+        <v>-0.1066</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.1028</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.0426</v>
+        <v>-4.2148</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.266</v>
+        <v>-0.2637</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.906</v>
+        <v>-10.8117</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.62</v>
       </c>
       <c r="I256" t="n">
-        <v>-1.0737</v>
+        <v>-0.9808</v>
       </c>
       <c r="J256" t="n">
-        <v>-44.0217</v>
+        <v>-40.2128</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.29</v>
       </c>
       <c r="I257" t="n">
-        <v>0.631</v>
+        <v>0.6046</v>
       </c>
       <c r="J257" t="n">
-        <v>25.871</v>
+        <v>24.7886</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.2469</v>
+        <v>0.248</v>
       </c>
       <c r="J258" t="n">
-        <v>10.1229</v>
+        <v>10.168</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.89</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1372</v>
+        <v>-0.152</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.6252</v>
+        <v>-6.232</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3179</v>
+        <v>-0.3315</v>
       </c>
       <c r="J260" t="n">
-        <v>-13.0339</v>
+        <v>-13.5915</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.65</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3747</v>
+        <v>-0.3863</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.3627</v>
+        <v>-15.8383</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.15</v>
       </c>
       <c r="I262" t="n">
-        <v>0.411</v>
+        <v>0.3947</v>
       </c>
       <c r="J262" t="n">
-        <v>9.864000000000001</v>
+        <v>9.472799999999999</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2157</v>
+        <v>0.2095</v>
       </c>
       <c r="J263" t="n">
-        <v>5.1768</v>
+        <v>5.028</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1494</v>
+        <v>-0.1668</v>
       </c>
       <c r="J264" t="n">
-        <v>-3.5856</v>
+        <v>-4.0032</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.6</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4092</v>
+        <v>-0.4214</v>
       </c>
       <c r="J265" t="n">
-        <v>-9.8208</v>
+        <v>-10.1136</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.48</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5198</v>
+        <v>-0.526</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.4752</v>
+        <v>-12.624</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>1.2123</v>
+        <v>1.1741</v>
       </c>
       <c r="J267" t="n">
-        <v>29.0952</v>
+        <v>28.1784</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1789</v>
+        <v>0.1879</v>
       </c>
       <c r="J268" t="n">
-        <v>4.2936</v>
+        <v>4.5096</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0203</v>
+        <v>-0.0139</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.4872</v>
+        <v>-0.3336</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1161</v>
+        <v>-0.1149</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.7864</v>
+        <v>-2.7576</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.89</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4032</v>
+        <v>-0.3862</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.6768</v>
+        <v>-9.268800000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.32</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6865</v>
+        <v>0.6544</v>
       </c>
       <c r="J272" t="n">
-        <v>19.9085</v>
+        <v>18.9776</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0148</v>
+        <v>0.0106</v>
       </c>
       <c r="J273" t="n">
-        <v>0.4292</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.88</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1474</v>
+        <v>-0.1626</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.2746</v>
+        <v>-4.7154</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.72</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3079</v>
+        <v>-0.3218</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.9291</v>
+        <v>-9.3322</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3365</v>
+        <v>-0.3496</v>
       </c>
       <c r="J276" t="n">
-        <v>-9.7585</v>
+        <v>-10.1384</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7386</v>
+        <v>0.6929</v>
       </c>
       <c r="J277" t="n">
-        <v>21.4194</v>
+        <v>20.0941</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.2535</v>
+        <v>0.255</v>
       </c>
       <c r="J278" t="n">
-        <v>7.3515</v>
+        <v>7.395</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0038</v>
+        <v>-0.0026</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.1102</v>
+        <v>-0.07539999999999999</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.235</v>
+        <v>-0.2345</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.815</v>
+        <v>-6.8005</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.495</v>
+        <v>-0.4734</v>
       </c>
       <c r="J281" t="n">
-        <v>-14.355</v>
+        <v>-13.7286</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0044</v>
+        <v>0.9437</v>
       </c>
       <c r="J282" t="n">
-        <v>26.1144</v>
+        <v>24.5362</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.91</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1098</v>
+        <v>-0.1253</v>
       </c>
       <c r="J283" t="n">
-        <v>-2.8548</v>
+        <v>-3.2578</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.8</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2224</v>
+        <v>-0.2395</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.7824</v>
+        <v>-6.227</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3384</v>
+        <v>-0.3529</v>
       </c>
       <c r="J285" t="n">
-        <v>-8.798400000000001</v>
+        <v>-9.1754</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.44</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5597</v>
+        <v>-0.5629</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.5522</v>
+        <v>-14.6354</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1653</v>
+        <v>1.1277</v>
       </c>
       <c r="J287" t="n">
-        <v>30.2978</v>
+        <v>29.3202</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0168</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="J288" t="n">
-        <v>26.4368</v>
+        <v>24.9392</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.15</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4448</v>
+        <v>0.4389</v>
       </c>
       <c r="J289" t="n">
-        <v>11.5648</v>
+        <v>11.4114</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3635</v>
+        <v>-0.3456</v>
       </c>
       <c r="J290" t="n">
-        <v>-9.451000000000001</v>
+        <v>-8.9856</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.6127</v>
+        <v>-0.5717</v>
       </c>
       <c r="J291" t="n">
-        <v>-15.9302</v>
+        <v>-14.8642</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.13</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4544</v>
+        <v>0.4189</v>
       </c>
       <c r="J292" t="n">
-        <v>10.4512</v>
+        <v>9.6347</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.7</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.2974</v>
+        <v>-0.3175</v>
       </c>
       <c r="J293" t="n">
-        <v>-6.8402</v>
+        <v>-7.3025</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.3986</v>
+        <v>-0.4147</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.1678</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4079</v>
+        <v>-0.4235</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.3817</v>
+        <v>-9.740500000000001</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.5</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4828</v>
+        <v>-0.494</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.1044</v>
+        <v>-11.362</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2627</v>
+        <v>1.2347</v>
       </c>
       <c r="J297" t="n">
-        <v>29.0421</v>
+        <v>28.3981</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.59</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2502</v>
+        <v>1.2214</v>
       </c>
       <c r="J298" t="n">
-        <v>28.7546</v>
+        <v>28.0922</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.0726</v>
+        <v>1.0285</v>
       </c>
       <c r="J299" t="n">
-        <v>24.6698</v>
+        <v>23.6555</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.4084</v>
+        <v>-0.3836</v>
       </c>
       <c r="J300" t="n">
-        <v>-9.3932</v>
+        <v>-8.822800000000001</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.2573</v>
+        <v>-1.1318</v>
       </c>
       <c r="J301" t="n">
-        <v>-28.9179</v>
+        <v>-26.0314</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0395</v>
+        <v>-0.0644</v>
       </c>
       <c r="J302" t="n">
-        <v>-0.869</v>
+        <v>-1.4168</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.1817</v>
+        <v>-0.2059</v>
       </c>
       <c r="J303" t="n">
-        <v>-3.9974</v>
+        <v>-4.5298</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.67</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3207</v>
+        <v>-0.3409</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.0554</v>
+        <v>-7.4998</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.64</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3471</v>
+        <v>-0.3666</v>
       </c>
       <c r="J305" t="n">
-        <v>-7.6362</v>
+        <v>-8.065200000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.29</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6748</v>
+        <v>-0.6726</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.8456</v>
+        <v>-14.7972</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.65</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2945</v>
+        <v>1.2739</v>
       </c>
       <c r="J307" t="n">
-        <v>28.479</v>
+        <v>28.0258</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.49</v>
       </c>
       <c r="I308" t="n">
-        <v>1.1001</v>
+        <v>1.065</v>
       </c>
       <c r="J308" t="n">
-        <v>24.2022</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.8534</v>
+        <v>0.8114</v>
       </c>
       <c r="J309" t="n">
-        <v>18.7748</v>
+        <v>17.8508</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.28</v>
       </c>
       <c r="I310" t="n">
-        <v>0.7215</v>
+        <v>0.6947</v>
       </c>
       <c r="J310" t="n">
-        <v>15.873</v>
+        <v>15.2834</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.251</v>
+        <v>-0.2292</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.522</v>
+        <v>-5.0424</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.23</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5535</v>
+        <v>0.5285</v>
       </c>
       <c r="J312" t="n">
-        <v>14.391</v>
+        <v>13.741</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.8</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2219</v>
+        <v>-0.2391</v>
       </c>
       <c r="J313" t="n">
-        <v>-5.7694</v>
+        <v>-6.2166</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.8</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2219</v>
+        <v>-0.2391</v>
       </c>
       <c r="J314" t="n">
-        <v>-5.7694</v>
+        <v>-6.2166</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.75</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2708</v>
+        <v>-0.2873</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.0408</v>
+        <v>-7.4698</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.2998</v>
+        <v>-0.3155</v>
       </c>
       <c r="J316" t="n">
-        <v>-7.7948</v>
+        <v>-8.202999999999999</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.64</v>
       </c>
       <c r="I317" t="n">
-        <v>1.3194</v>
+        <v>1.2937</v>
       </c>
       <c r="J317" t="n">
-        <v>34.3044</v>
+        <v>33.6362</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.33</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8633999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="J318" t="n">
-        <v>22.4484</v>
+        <v>21.164</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.6784</v>
+        <v>0.651</v>
       </c>
       <c r="J319" t="n">
-        <v>17.6384</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4885</v>
+        <v>0.4801</v>
       </c>
       <c r="J320" t="n">
-        <v>12.701</v>
+        <v>12.4826</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-1.1838</v>
+        <v>-1.0694</v>
       </c>
       <c r="J321" t="n">
-        <v>-30.7788</v>
+        <v>-27.8044</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1853/event_1853_evp_summary.xlsx
+++ b/database/event/1853/event_1853_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8635</v>
+        <v>7.0402</v>
       </c>
       <c r="C2" t="n">
-        <v>2.3464</v>
+        <v>2.4068</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5002</v>
+        <v>2.6014</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8635</v>
+        <v>7.0402</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8932</v>
+        <v>2.8911</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9703</v>
+        <v>4.1491</v>
       </c>
       <c r="H2" t="n">
-        <v>4.6516</v>
+        <v>4.4118</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5118</v>
+        <v>2.4771</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9703</v>
+        <v>4.1491</v>
       </c>
       <c r="K2" t="n">
         <v>156</v>
@@ -529,7 +529,7 @@
         <v>123</v>
       </c>
       <c r="M2" t="n">
-        <v>6.4821</v>
+        <v>6.6262</v>
       </c>
       <c r="N2" t="n">
         <v>279</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.9828</v>
+        <v>5.9711</v>
       </c>
       <c r="C3" t="n">
-        <v>2.0453</v>
+        <v>2.0413</v>
       </c>
       <c r="D3" t="n">
-        <v>2.0993</v>
+        <v>2.1143</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9828</v>
+        <v>5.9711</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5519</v>
+        <v>2.6312</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4309</v>
+        <v>3.3399</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5254</v>
+        <v>3.4362</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9037</v>
+        <v>1.9293</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4309</v>
+        <v>3.3399</v>
       </c>
       <c r="K3" t="n">
         <v>156</v>
@@ -575,7 +575,7 @@
         <v>123</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3346</v>
+        <v>5.2692</v>
       </c>
       <c r="N3" t="n">
         <v>279</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5913</v>
+        <v>4.4752</v>
       </c>
       <c r="C4" t="n">
-        <v>1.5696</v>
+        <v>1.5299</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4659</v>
+        <v>1.4329</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5913</v>
+        <v>4.4752</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0525</v>
+        <v>3.9032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="H4" t="n">
-        <v>8.4764</v>
+        <v>8.2117</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5772</v>
+        <v>4.6106</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.572</v>
       </c>
       <c r="K4" t="n">
         <v>100</v>
@@ -621,7 +621,7 @@
         <v>146</v>
       </c>
       <c r="M4" t="n">
-        <v>5.116000000000001</v>
+        <v>5.1826</v>
       </c>
       <c r="N4" t="n">
         <v>246</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8064</v>
+        <v>2.8005</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9594</v>
+        <v>0.9574</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6533</v>
+        <v>0.67</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8064</v>
+        <v>2.8005</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0915</v>
+        <v>3.0356</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2851</v>
+        <v>-0.2351</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3058</v>
+        <v>4.9545</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8651</v>
+        <v>2.7818</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2851</v>
+        <v>-0.2351</v>
       </c>
       <c r="K5" t="n">
         <v>100</v>
@@ -667,7 +667,7 @@
         <v>146</v>
       </c>
       <c r="M5" t="n">
-        <v>2.58</v>
+        <v>2.5467</v>
       </c>
       <c r="N5" t="n">
         <v>246</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>coldzera</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.732</v>
+        <v>2.734</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9347</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6397</v>
       </c>
       <c r="E6" t="n">
-        <v>2.732</v>
+        <v>2.734</v>
       </c>
       <c r="F6" t="n">
-        <v>2.732</v>
+        <v>2.5559</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.1781</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2546</v>
+        <v>3.1535</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2546</v>
+        <v>1.7706</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.1781</v>
       </c>
       <c r="K6" t="n">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2546</v>
+        <v>1.9487</v>
       </c>
       <c r="N6" t="n">
-        <v>183</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>coldzera</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.6939</v>
+        <v>2.6766</v>
       </c>
       <c r="C7" t="n">
-        <v>0.921</v>
+        <v>0.9151</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6021</v>
+        <v>0.6135</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6939</v>
+        <v>2.6766</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4763</v>
+        <v>2.6766</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2176</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2762</v>
+        <v>3.1837</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7691</v>
+        <v>3.1837</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2176</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="L7" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.9867</v>
+        <v>3.1837</v>
       </c>
       <c r="N7" t="n">
-        <v>304</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.442</v>
+        <v>2.4065</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8348</v>
+        <v>0.8227</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4874</v>
+        <v>0.4905</v>
       </c>
       <c r="E8" t="n">
-        <v>2.442</v>
+        <v>2.4065</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1428</v>
+        <v>2.1162</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2992</v>
+        <v>0.2903</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1756</v>
+        <v>2.1162</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1748</v>
+        <v>1.1882</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2992</v>
+        <v>0.2903</v>
       </c>
       <c r="K8" t="n">
         <v>212</v>
@@ -805,7 +805,7 @@
         <v>55</v>
       </c>
       <c r="M8" t="n">
-        <v>1.474</v>
+        <v>1.4785</v>
       </c>
       <c r="N8" t="n">
         <v>267</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.4024</v>
+        <v>2.2052</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8213</v>
+        <v>0.7539</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4694</v>
+        <v>0.3988</v>
       </c>
       <c r="E9" t="n">
-        <v>2.4024</v>
+        <v>2.2052</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4024</v>
+        <v>2.2052</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5331</v>
+        <v>2.2052</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5331</v>
+        <v>2.2052</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5331</v>
+        <v>2.2052</v>
       </c>
       <c r="N9" t="n">
         <v>240</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.2469</v>
+        <v>2.1659</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7681</v>
+        <v>0.7405</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3986</v>
+        <v>0.3809</v>
       </c>
       <c r="E10" t="n">
-        <v>2.2469</v>
+        <v>2.1659</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2469</v>
+        <v>2.493</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0.3271</v>
       </c>
       <c r="H10" t="n">
-        <v>2.2469</v>
+        <v>2.9173</v>
       </c>
       <c r="I10" t="n">
-        <v>2.2469</v>
+        <v>1.638</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0.3271</v>
       </c>
       <c r="K10" t="n">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2469</v>
+        <v>1.3109</v>
       </c>
       <c r="N10" t="n">
-        <v>183</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.173</v>
+        <v>2.1658</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7429</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>0.365</v>
+        <v>0.3808</v>
       </c>
       <c r="E11" t="n">
-        <v>2.173</v>
+        <v>2.1658</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4806</v>
+        <v>2.1658</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6924</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4806</v>
+        <v>2.1658</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7995</v>
+        <v>2.1658</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6924</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="L11" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4919</v>
+        <v>2.1658</v>
       </c>
       <c r="N11" t="n">
-        <v>304</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0783</v>
+        <v>2.1577</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7105</v>
+        <v>0.7377</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3219</v>
+        <v>0.3771</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0783</v>
+        <v>2.1577</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8896</v>
+        <v>2.9105</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8113</v>
+        <v>-0.7528</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6397</v>
+        <v>4.4845</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5054</v>
+        <v>2.5179</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8113</v>
+        <v>-0.7528</v>
       </c>
       <c r="K12" t="n">
         <v>100</v>
@@ -989,7 +989,7 @@
         <v>146</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6941</v>
+        <v>1.7651</v>
       </c>
       <c r="N12" t="n">
         <v>246</v>
@@ -998,47 +998,47 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0349</v>
+        <v>1.8884</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6957</v>
+        <v>0.6456</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3021</v>
+        <v>0.2545</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0349</v>
+        <v>1.8884</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4112</v>
+        <v>1.2515</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3763</v>
+        <v>0.6369</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0613</v>
+        <v>1.2515</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6531</v>
+        <v>0.7027</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3763</v>
+        <v>0.6369</v>
       </c>
       <c r="K13" t="n">
-        <v>156</v>
+        <v>226</v>
       </c>
       <c r="L13" t="n">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2768</v>
+        <v>1.3396</v>
       </c>
       <c r="N13" t="n">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5716</v>
+        <v>1.5459</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5373</v>
+        <v>0.5285</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0912</v>
+        <v>0.0984</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5716</v>
+        <v>1.5459</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1735</v>
+        <v>1.1602</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3981</v>
+        <v>0.3857</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1735</v>
+        <v>1.1602</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6337</v>
+        <v>0.6514</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3981</v>
+        <v>0.3857</v>
       </c>
       <c r="K14" t="n">
         <v>212</v>
@@ -1081,7 +1081,7 @@
         <v>55</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0318</v>
+        <v>1.0371</v>
       </c>
       <c r="N14" t="n">
         <v>267</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.256</v>
+        <v>1.3062</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4294</v>
+        <v>0.4466</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0524</v>
+        <v>-0.0108</v>
       </c>
       <c r="E15" t="n">
-        <v>1.256</v>
+        <v>1.3062</v>
       </c>
       <c r="F15" t="n">
-        <v>1.256</v>
+        <v>1.8238</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.256</v>
+        <v>1.8238</v>
       </c>
       <c r="I15" t="n">
-        <v>1.256</v>
+        <v>1.024</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>129</v>
+        <v>226</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="M15" t="n">
-        <v>1.256</v>
+        <v>0.5064000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2553</v>
+        <v>1.1511</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4291</v>
+        <v>0.3935</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0528</v>
+        <v>-0.0814</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2553</v>
+        <v>1.1511</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7356</v>
+        <v>1.1511</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4803</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7356</v>
+        <v>1.1511</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9372</v>
+        <v>1.1511</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4803</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>226</v>
+        <v>129</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4569</v>
+        <v>1.1511</v>
       </c>
       <c r="N16" t="n">
-        <v>304</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>flamie</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1638</v>
+        <v>1.1344</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3979</v>
+        <v>0.3878</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0944</v>
+        <v>-0.089</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1638</v>
+        <v>1.1344</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1638</v>
+        <v>1.0781</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1638</v>
+        <v>1.0781</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1638</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.0563</v>
       </c>
       <c r="K17" t="n">
-        <v>129</v>
+        <v>212</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1638</v>
+        <v>0.6616</v>
       </c>
       <c r="N17" t="n">
-        <v>129</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flamie</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.161</v>
+        <v>0.9437</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3969</v>
+        <v>0.3226</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.1759</v>
       </c>
       <c r="E18" t="n">
-        <v>1.161</v>
+        <v>0.9437</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0659</v>
+        <v>0.9437</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0951</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0659</v>
+        <v>0.9437</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5756</v>
+        <v>0.9437</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0951</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6707</v>
+        <v>0.9437</v>
       </c>
       <c r="N18" t="n">
-        <v>267</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9096</v>
+        <v>0.8541</v>
       </c>
       <c r="C19" t="n">
-        <v>0.311</v>
+        <v>0.292</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2101</v>
+        <v>-0.2167</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9096</v>
+        <v>0.8541</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8156</v>
+        <v>0.7778</v>
       </c>
       <c r="G19" t="n">
-        <v>0.094</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8156</v>
+        <v>0.7778</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4404</v>
+        <v>0.4367</v>
       </c>
       <c r="J19" t="n">
-        <v>0.094</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>226</v>
@@ -1311,7 +1311,7 @@
         <v>78</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5344</v>
+        <v>0.513</v>
       </c>
       <c r="N19" t="n">
         <v>304</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2783</v>
+        <v>0.2505</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2537</v>
+        <v>-0.272</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7327</v>
       </c>
       <c r="N20" t="n">
         <v>120</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2181</v>
+        <v>0.2224</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3338</v>
+        <v>-0.3094</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6379</v>
+        <v>0.6506</v>
       </c>
       <c r="N21" t="n">
         <v>183</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3216</v>
+        <v>0.2503</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1099</v>
+        <v>0.0856</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4778</v>
+        <v>-0.4918</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3216</v>
+        <v>0.2503</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1839</v>
+        <v>0.1395</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1377</v>
+        <v>0.1108</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1839</v>
+        <v>0.1395</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0993</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1377</v>
+        <v>0.1108</v>
       </c>
       <c r="K22" t="n">
         <v>212</v>
@@ -1449,7 +1449,7 @@
         <v>55</v>
       </c>
       <c r="M22" t="n">
-        <v>0.237</v>
+        <v>0.1891</v>
       </c>
       <c r="N22" t="n">
         <v>267</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0766</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4955</v>
+        <v>-0.5037</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2828</v>
+        <v>0.2241</v>
       </c>
       <c r="N23" t="n">
         <v>183</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0224</v>
+        <v>0.0125</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5944</v>
+        <v>-0.5891</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0654</v>
+        <v>0.0367</v>
       </c>
       <c r="N24" t="n">
         <v>120</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0538</v>
+        <v>-0.028</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.6958</v>
+        <v>-0.6431</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1573</v>
+        <v>-0.0818</v>
       </c>
       <c r="N25" t="n">
         <v>240</v>
@@ -1596,139 +1596,139 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>seized</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.2993</v>
+        <v>-0.2155</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1023</v>
+        <v>-0.0737</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.7605</v>
+        <v>-0.704</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.2993</v>
+        <v>-0.2155</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2993</v>
+        <v>-1.2113</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.9958</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2993</v>
+        <v>-1.2113</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2993</v>
+        <v>-0.6801</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.9958</v>
       </c>
       <c r="K26" t="n">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2993</v>
+        <v>0.3157</v>
       </c>
       <c r="N26" t="n">
-        <v>129</v>
+        <v>279</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>Pimp</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3277</v>
+        <v>-0.2369</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.112</v>
+        <v>-0.081</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.7734</v>
+        <v>-0.7137</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3277</v>
+        <v>-0.2369</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.3393</v>
+        <v>-0.2369</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0116</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.3393</v>
+        <v>-0.2369</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7232</v>
+        <v>-0.2369</v>
       </c>
       <c r="J27" t="n">
-        <v>1.0116</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>156</v>
+        <v>240</v>
       </c>
       <c r="L27" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2884000000000001</v>
+        <v>-0.2369</v>
       </c>
       <c r="N27" t="n">
-        <v>279</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pimp</t>
+          <t>seized</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1173</v>
+        <v>-0.1182</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7803</v>
+        <v>-0.7633</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.343</v>
+        <v>-0.3457</v>
       </c>
       <c r="N28" t="n">
-        <v>240</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29">
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1457</v>
+        <v>-0.1289</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.8183</v>
+        <v>-0.7776</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4263</v>
+        <v>-0.3771</v>
       </c>
       <c r="N29" t="n">
         <v>120</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1566</v>
+        <v>-0.1537</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.8328</v>
+        <v>-0.8106</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4582</v>
+        <v>-0.4496</v>
       </c>
       <c r="N30" t="n">
         <v>129</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2152</v>
+        <v>-0.2237</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.9108000000000001</v>
+        <v>-0.9038</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6296</v>
+        <v>-0.6542</v>
       </c>
       <c r="N31" t="n">
         <v>120</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.2958</v>
+        <v>-0.3133</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.0181</v>
+        <v>-1.0233</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8653</v>
+        <v>-0.9164</v>
       </c>
       <c r="N32" t="n">
         <v>240</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.3189</v>
+        <v>-0.3162</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.0489</v>
+        <v>-1.0271</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.9329</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>120</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.335</v>
+        <v>-0.3234</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0702</v>
+        <v>-1.0367</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9798</v>
+        <v>-0.9459</v>
       </c>
       <c r="N34" t="n">
         <v>240</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.4439</v>
+        <v>-1.3153</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.4936</v>
+        <v>-0.4497</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.2815</v>
+        <v>-1.205</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.4439</v>
+        <v>-1.3153</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.4187</v>
+        <v>-1.2727</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.0252</v>
+        <v>-0.0426</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.4187</v>
+        <v>-1.2727</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7661</v>
+        <v>-0.7146</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.0252</v>
+        <v>-0.0426</v>
       </c>
       <c r="K35" t="n">
         <v>156</v>
@@ -2047,7 +2047,7 @@
         <v>123</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7913</v>
+        <v>-0.7572</v>
       </c>
       <c r="N35" t="n">
         <v>279</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.524</v>
+        <v>-0.5424</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.3219</v>
+        <v>-1.3286</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.5326</v>
+        <v>-1.5867</v>
       </c>
       <c r="N36" t="n">
         <v>183</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.5835</v>
+        <v>-0.5626</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.4011</v>
+        <v>-1.3554</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.7067</v>
+        <v>-1.6456</v>
       </c>
       <c r="N37" t="n">
         <v>129</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-2.6419</v>
+        <v>-2.3803</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.9032</v>
+        <v>-0.8138</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.8269</v>
+        <v>-1.6901</v>
       </c>
       <c r="E38" t="n">
-        <v>-2.6419</v>
+        <v>-2.3803</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4026</v>
+        <v>-1.1823</v>
       </c>
       <c r="G38" t="n">
-        <v>-1.2393</v>
+        <v>-1.198</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.4026</v>
+        <v>-1.1823</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7574</v>
+        <v>-0.6637999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>-1.2393</v>
+        <v>-1.198</v>
       </c>
       <c r="K38" t="n">
         <v>100</v>
@@ -2185,7 +2185,7 @@
         <v>146</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.9967</v>
+        <v>-1.8618</v>
       </c>
       <c r="N38" t="n">
         <v>246</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-5.1236</v>
+        <v>-4.8135</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.7516</v>
+        <v>-1.6456</v>
       </c>
       <c r="D39" t="n">
-        <v>-2.9566</v>
+        <v>-2.7986</v>
       </c>
       <c r="E39" t="n">
-        <v>-5.1236</v>
+        <v>-4.8135</v>
       </c>
       <c r="F39" t="n">
-        <v>-4.6399</v>
+        <v>-4.3007</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4837</v>
+        <v>-0.5128</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.6399</v>
+        <v>-4.3007</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.5055</v>
+        <v>-2.4147</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4837</v>
+        <v>-0.5128</v>
       </c>
       <c r="K39" t="n">
         <v>100</v>
@@ -2231,7 +2231,7 @@
         <v>146</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.9892</v>
+        <v>-2.9275</v>
       </c>
       <c r="N39" t="n">
         <v>246</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-5.143</v>
+        <v>-5.101</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.7582</v>
+        <v>-1.7439</v>
       </c>
       <c r="D40" t="n">
-        <v>-2.9654</v>
+        <v>-2.9295</v>
       </c>
       <c r="E40" t="n">
-        <v>-5.143</v>
+        <v>-5.101</v>
       </c>
       <c r="F40" t="n">
-        <v>-4.143</v>
+        <v>-4.101</v>
       </c>
       <c r="G40" t="n">
         <v>-1</v>
       </c>
       <c r="H40" t="n">
-        <v>-4.143</v>
+        <v>-4.101</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.2372</v>
+        <v>-2.3026</v>
       </c>
       <c r="J40" t="n">
         <v>-1</v>
@@ -2277,7 +2277,7 @@
         <v>78</v>
       </c>
       <c r="M40" t="n">
-        <v>-3.2372</v>
+        <v>-3.3026</v>
       </c>
       <c r="N40" t="n">
         <v>304</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-9.0519</v>
+        <v>-8.5441</v>
       </c>
       <c r="C41" t="n">
-        <v>-3.0946</v>
+        <v>-2.921</v>
       </c>
       <c r="D41" t="n">
-        <v>-4.7448</v>
+        <v>-4.498</v>
       </c>
       <c r="E41" t="n">
-        <v>-9.0519</v>
+        <v>-8.5441</v>
       </c>
       <c r="F41" t="n">
-        <v>-8.4961</v>
+        <v>-8.008800000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5558</v>
+        <v>-0.5353</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.4961</v>
+        <v>-8.008800000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.5878</v>
+        <v>-4.4967</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5558</v>
+        <v>-0.5353</v>
       </c>
       <c r="K41" t="n">
         <v>212</v>
@@ -2323,7 +2323,7 @@
         <v>55</v>
       </c>
       <c r="M41" t="n">
-        <v>-5.143599999999999</v>
+        <v>-5.032</v>
       </c>
       <c r="N41" t="n">
         <v>267</v>
@@ -2429,10 +2429,10 @@
         <v>1.82</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6567</v>
+        <v>1.6896</v>
       </c>
       <c r="J2" t="n">
-        <v>39.7608</v>
+        <v>40.5504</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.24</v>
       </c>
       <c r="I3" t="n">
-        <v>0.626</v>
+        <v>0.5952</v>
       </c>
       <c r="J3" t="n">
-        <v>15.024</v>
+        <v>14.2848</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4984</v>
+        <v>0.4652</v>
       </c>
       <c r="J4" t="n">
-        <v>11.9616</v>
+        <v>11.1648</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.03</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0993</v>
+        <v>0.0789</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3832</v>
+        <v>1.8936</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.87</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4625</v>
+        <v>-0.4228</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.1</v>
+        <v>-10.1472</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.239</v>
+        <v>0.2034</v>
       </c>
       <c r="J7" t="n">
-        <v>5.736</v>
+        <v>4.8816</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1453</v>
+        <v>-0.1299</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.4872</v>
+        <v>-3.1176</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.76</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2683</v>
+        <v>-0.2522</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.4392</v>
+        <v>-6.0528</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3316</v>
+        <v>-0.3165</v>
       </c>
       <c r="J10" t="n">
-        <v>-7.9584</v>
+        <v>-7.596</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.38</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6038</v>
+        <v>-0.6181</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.4912</v>
+        <v>-14.8344</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5271</v>
+        <v>1.5592</v>
       </c>
       <c r="J12" t="n">
-        <v>36.6504</v>
+        <v>37.4208</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>16.9224</v>
+        <v>16.2696</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.18</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4959</v>
+        <v>0.4634</v>
       </c>
       <c r="J14" t="n">
-        <v>11.9016</v>
+        <v>11.1216</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4732</v>
+        <v>0.4404</v>
       </c>
       <c r="J15" t="n">
-        <v>11.3568</v>
+        <v>10.5696</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.87</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4655</v>
+        <v>-0.4263</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.172</v>
+        <v>-10.2312</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>0.93</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0762</v>
+        <v>-0.0611</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.8288</v>
+        <v>-1.4664</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.87</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1494</v>
+        <v>-0.1336</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.5856</v>
+        <v>-3.2064</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.66</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3541</v>
+        <v>-0.3407</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.4984</v>
+        <v>-8.1768</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.58</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4253</v>
+        <v>-0.4161</v>
       </c>
       <c r="J20" t="n">
-        <v>-10.2072</v>
+        <v>-9.9864</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.53</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4695</v>
+        <v>-0.4644</v>
       </c>
       <c r="J21" t="n">
-        <v>-11.268</v>
+        <v>-11.1456</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.76</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J22" t="n">
-        <v>36.906</v>
+        <v>39.644</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.31</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7498</v>
+        <v>0.7313</v>
       </c>
       <c r="J23" t="n">
-        <v>14.996</v>
+        <v>14.626</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.98</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1643</v>
+        <v>-0.1403</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.286</v>
+        <v>-2.806</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.98</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1643</v>
+        <v>-0.1403</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.286</v>
+        <v>-2.806</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.87</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.486</v>
+        <v>-0.4513</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.720000000000001</v>
+        <v>-9.026</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.2098</v>
+        <v>-0.1943</v>
       </c>
       <c r="J27" t="n">
-        <v>-4.196</v>
+        <v>-3.886</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.72</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2911</v>
+        <v>-0.2789</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.822</v>
+        <v>-5.578</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.59</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4066</v>
+        <v>-0.3975</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.132</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.57</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4241</v>
+        <v>-0.4159</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.481999999999999</v>
+        <v>-8.318</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.51</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4769</v>
+        <v>-0.4726</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.538</v>
+        <v>-9.452</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0275</v>
+        <v>1.017</v>
       </c>
       <c r="J32" t="n">
-        <v>27.7425</v>
+        <v>27.459</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.44</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8874</v>
+        <v>0.8722</v>
       </c>
       <c r="J33" t="n">
-        <v>23.9598</v>
+        <v>23.5494</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5238</v>
+        <v>0.5123</v>
       </c>
       <c r="J34" t="n">
-        <v>14.1426</v>
+        <v>13.8321</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.91</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3416</v>
+        <v>-0.2998</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.2232</v>
+        <v>-8.0946</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.59</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0607</v>
+        <v>-1.0688</v>
       </c>
       <c r="J36" t="n">
-        <v>-28.6389</v>
+        <v>-28.8576</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2874</v>
+        <v>0.2399</v>
       </c>
       <c r="J37" t="n">
-        <v>7.7598</v>
+        <v>6.4773</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.02</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1006</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>2.7162</v>
+        <v>2.0223</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1475</v>
+        <v>-0.1307</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.9825</v>
+        <v>-3.5289</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.71</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3246</v>
+        <v>-0.3079</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.764200000000001</v>
+        <v>-8.3133</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.57</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4506</v>
+        <v>-0.4443</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.1662</v>
+        <v>-11.9961</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2502</v>
+        <v>0.2392</v>
       </c>
       <c r="J42" t="n">
-        <v>6.0048</v>
+        <v>5.7408</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.2011</v>
+        <v>0.1876</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8264</v>
+        <v>4.5024</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.87</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.166</v>
+        <v>-0.1493</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.984</v>
+        <v>-3.5832</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.68</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3486</v>
+        <v>-0.3333</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.366400000000001</v>
+        <v>-7.9992</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.38</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6101</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>-14.6424</v>
+        <v>-15.036</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.66</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7015</v>
+        <v>0.6573</v>
       </c>
       <c r="J47" t="n">
-        <v>16.836</v>
+        <v>15.7752</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.26</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3729</v>
+        <v>0.3123</v>
       </c>
       <c r="J48" t="n">
-        <v>8.9496</v>
+        <v>7.4952</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.23</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3379</v>
+        <v>0.2803</v>
       </c>
       <c r="J49" t="n">
-        <v>8.1096</v>
+        <v>6.7272</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.92</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1363</v>
+        <v>-0.1172</v>
       </c>
       <c r="J50" t="n">
-        <v>-3.2712</v>
+        <v>-2.8128</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3599</v>
+        <v>-0.3477</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.637600000000001</v>
+        <v>-8.344799999999999</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.91</v>
       </c>
       <c r="I52" t="n">
-        <v>1.5022</v>
+        <v>1.5306</v>
       </c>
       <c r="J52" t="n">
-        <v>40.5594</v>
+        <v>41.3262</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4874</v>
+        <v>0.4684</v>
       </c>
       <c r="J53" t="n">
-        <v>13.1598</v>
+        <v>12.6468</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.07</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2337</v>
+        <v>0.2034</v>
       </c>
       <c r="J54" t="n">
-        <v>6.3099</v>
+        <v>5.4918</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.88</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.427</v>
+        <v>-0.3854</v>
       </c>
       <c r="J55" t="n">
-        <v>-11.529</v>
+        <v>-10.4058</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5971</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.1217</v>
+        <v>-15.147</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>0.99</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0078</v>
+        <v>-0.0035</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.2106</v>
+        <v>-0.0945</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.96</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0571</v>
+        <v>-0.0464</v>
       </c>
       <c r="J58" t="n">
-        <v>-1.5417</v>
+        <v>-1.2528</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.92</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1097</v>
+        <v>-0.0953</v>
       </c>
       <c r="J59" t="n">
-        <v>-2.9619</v>
+        <v>-2.5731</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3676</v>
+        <v>-0.3536</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.9252</v>
+        <v>-9.5472</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.63</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3947</v>
+        <v>-0.3828</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.6569</v>
+        <v>-10.3356</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.33</v>
       </c>
       <c r="I62" t="n">
-        <v>0.7469</v>
+        <v>0.7313</v>
       </c>
       <c r="J62" t="n">
-        <v>19.4194</v>
+        <v>19.0138</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5046</v>
+        <v>0.4861</v>
       </c>
       <c r="J63" t="n">
-        <v>13.1196</v>
+        <v>12.6386</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3578</v>
+        <v>0.317</v>
       </c>
       <c r="J64" t="n">
-        <v>9.3028</v>
+        <v>8.242000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.5026</v>
+        <v>-0.4606</v>
       </c>
       <c r="J65" t="n">
-        <v>-13.0676</v>
+        <v>-11.9756</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.77</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6652</v>
+        <v>-0.6304</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.2952</v>
+        <v>-16.3904</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.42</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7058</v>
+        <v>0.6757</v>
       </c>
       <c r="J67" t="n">
-        <v>18.3508</v>
+        <v>17.5682</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.23</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4827</v>
+        <v>0.4405</v>
       </c>
       <c r="J68" t="n">
-        <v>12.5502</v>
+        <v>11.453</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.82</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2276</v>
+        <v>-0.2073</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.9176</v>
+        <v>-5.3898</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.7</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3429</v>
+        <v>-0.3274</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.9154</v>
+        <v>-8.5124</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.459</v>
+        <v>-0.4547</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.934</v>
+        <v>-11.8222</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.26</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6375999999999999</v>
+        <v>0.6234</v>
       </c>
       <c r="J72" t="n">
-        <v>18.4904</v>
+        <v>18.0786</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.21</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5558</v>
+        <v>0.5444</v>
       </c>
       <c r="J73" t="n">
-        <v>16.1182</v>
+        <v>15.7876</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.05</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1934</v>
+        <v>0.1616</v>
       </c>
       <c r="J74" t="n">
-        <v>5.6086</v>
+        <v>4.6864</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.03</v>
       </c>
       <c r="I75" t="n">
-        <v>0.1301</v>
+        <v>0.1049</v>
       </c>
       <c r="J75" t="n">
-        <v>3.7729</v>
+        <v>3.0421</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.67</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.8813</v>
+        <v>-0.8649</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.5577</v>
+        <v>-25.0821</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.27</v>
       </c>
       <c r="I77" t="n">
-        <v>0.5268</v>
+        <v>0.4976</v>
       </c>
       <c r="J77" t="n">
-        <v>15.2772</v>
+        <v>14.4304</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.2</v>
       </c>
       <c r="I78" t="n">
-        <v>0.438</v>
+        <v>0.3837</v>
       </c>
       <c r="J78" t="n">
-        <v>12.702</v>
+        <v>11.1273</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0968</v>
+        <v>-0.0806</v>
       </c>
       <c r="J79" t="n">
-        <v>-2.8072</v>
+        <v>-2.3374</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.74</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3077</v>
+        <v>-0.29</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.923299999999999</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.7</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.345</v>
+        <v>-0.3297</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.005</v>
+        <v>-9.561299999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.27</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5879</v>
+        <v>0.5345</v>
       </c>
       <c r="J82" t="n">
-        <v>14.6975</v>
+        <v>13.3625</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.85</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.191</v>
+        <v>-0.1719</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.775</v>
+        <v>-4.2975</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.8</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2412</v>
+        <v>-0.2217</v>
       </c>
       <c r="J84" t="n">
-        <v>-6.03</v>
+        <v>-5.5425</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.77</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2704</v>
+        <v>-0.2514</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.76</v>
+        <v>-6.285</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3178</v>
+        <v>-0.3006</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.945</v>
+        <v>-7.515</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.52</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1637</v>
+        <v>1.18</v>
       </c>
       <c r="J87" t="n">
-        <v>29.0925</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.13</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4018</v>
+        <v>0.3615</v>
       </c>
       <c r="J88" t="n">
-        <v>10.045</v>
+        <v>9.0375</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.02</v>
       </c>
       <c r="I89" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.0703</v>
       </c>
       <c r="J89" t="n">
-        <v>2.2225</v>
+        <v>1.7575</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.95</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2148</v>
+        <v>-0.1781</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.37</v>
+        <v>-4.4525</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.77</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6715</v>
+        <v>-0.6377</v>
       </c>
       <c r="J91" t="n">
-        <v>-16.7875</v>
+        <v>-15.9425</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.45</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5978</v>
+        <v>0.5278</v>
       </c>
       <c r="J92" t="n">
-        <v>24.5098</v>
+        <v>21.6398</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.09</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1659</v>
+        <v>0.1276</v>
       </c>
       <c r="J93" t="n">
-        <v>6.8019</v>
+        <v>5.2316</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.99</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0298</v>
+        <v>-0.0212</v>
       </c>
       <c r="J94" t="n">
-        <v>-1.2218</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.141</v>
+        <v>-0.1214</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.781</v>
+        <v>-4.9774</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.89</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.1639</v>
+        <v>-0.1436</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.7199</v>
+        <v>-5.8876</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.18</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3339</v>
+        <v>0.3262</v>
       </c>
       <c r="J97" t="n">
-        <v>13.6899</v>
+        <v>13.3742</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.17</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3197</v>
+        <v>0.3108</v>
       </c>
       <c r="J98" t="n">
-        <v>13.1077</v>
+        <v>12.7428</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.87</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1715</v>
+        <v>-0.1526</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.0315</v>
+        <v>-6.2566</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.82</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2231</v>
+        <v>-0.2032</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.1471</v>
+        <v>-8.331200000000001</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.46</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.549</v>
+        <v>-0.5564</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.509</v>
+        <v>-22.8124</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.2</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4624</v>
+        <v>0.4068</v>
       </c>
       <c r="J102" t="n">
-        <v>13.4096</v>
+        <v>11.7972</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.05</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1677</v>
+        <v>0.1304</v>
       </c>
       <c r="J103" t="n">
-        <v>4.8633</v>
+        <v>3.7816</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0153</v>
+        <v>0.0107</v>
       </c>
       <c r="J104" t="n">
-        <v>0.4437</v>
+        <v>0.3103</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.67</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3655</v>
+        <v>-0.3514</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.5995</v>
+        <v>-10.1906</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.57</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4545</v>
+        <v>-0.4491</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.1805</v>
+        <v>-13.0239</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.36</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8837</v>
+        <v>0.8643</v>
       </c>
       <c r="J107" t="n">
-        <v>25.6273</v>
+        <v>25.0647</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.31</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7831</v>
+        <v>0.7562</v>
       </c>
       <c r="J108" t="n">
-        <v>22.7099</v>
+        <v>21.9298</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.3175</v>
+        <v>0.2832</v>
       </c>
       <c r="J109" t="n">
-        <v>9.2075</v>
+        <v>8.2128</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.09</v>
       </c>
       <c r="I110" t="n">
-        <v>0.2912</v>
+        <v>0.2579</v>
       </c>
       <c r="J110" t="n">
-        <v>8.444800000000001</v>
+        <v>7.4791</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.91</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3449</v>
+        <v>-0.3033</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.0021</v>
+        <v>-8.7957</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.38</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7802</v>
+        <v>0.7401</v>
       </c>
       <c r="J112" t="n">
-        <v>21.0654</v>
+        <v>19.9827</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.89</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1469</v>
+        <v>-0.1303</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.9663</v>
+        <v>-3.5181</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.87</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1686</v>
+        <v>-0.1511</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.5522</v>
+        <v>-4.0797</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.62</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4058</v>
+        <v>-0.3949</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.9566</v>
+        <v>-10.6623</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.5</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5107</v>
+        <v>-0.5119</v>
       </c>
       <c r="J116" t="n">
-        <v>-13.7889</v>
+        <v>-13.8213</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.52</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1348</v>
+        <v>1.1475</v>
       </c>
       <c r="J117" t="n">
-        <v>30.6396</v>
+        <v>30.9825</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.39</v>
       </c>
       <c r="I118" t="n">
-        <v>0.9337</v>
+        <v>0.92</v>
       </c>
       <c r="J118" t="n">
-        <v>25.2099</v>
+        <v>24.84</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5464</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>14.7528</v>
+        <v>13.8132</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.02</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0701</v>
+        <v>0.0539</v>
       </c>
       <c r="J120" t="n">
-        <v>1.8927</v>
+        <v>1.4553</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.623</v>
+        <v>-0.5887</v>
       </c>
       <c r="J121" t="n">
-        <v>-16.821</v>
+        <v>-15.8949</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.49</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6437</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J122" t="n">
-        <v>17.3799</v>
+        <v>15.5007</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.14</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2367</v>
+        <v>0.1881</v>
       </c>
       <c r="J123" t="n">
-        <v>6.3909</v>
+        <v>5.0787</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.02</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0511</v>
+        <v>0.0353</v>
       </c>
       <c r="J124" t="n">
-        <v>1.3797</v>
+        <v>0.9530999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.88</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1738</v>
+        <v>-0.1533</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.6926</v>
+        <v>-4.1391</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.73</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3243</v>
+        <v>-0.3083</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.7561</v>
+        <v>-8.3241</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.09</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2029</v>
+        <v>0.1869</v>
       </c>
       <c r="J127" t="n">
-        <v>5.4783</v>
+        <v>5.0463</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.93</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J128" t="n">
-        <v>-2.7891</v>
+        <v>-2.3922</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.93</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.1033</v>
+        <v>-0.0886</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.7891</v>
+        <v>-2.3922</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.89</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1494</v>
+        <v>-0.1318</v>
       </c>
       <c r="J130" t="n">
-        <v>-4.0338</v>
+        <v>-3.5586</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.58</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4444</v>
+        <v>-0.4377</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.9988</v>
+        <v>-11.8179</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.14</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3297</v>
+        <v>0.277</v>
       </c>
       <c r="J132" t="n">
-        <v>9.891</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.13</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3112</v>
+        <v>0.2598</v>
       </c>
       <c r="J133" t="n">
-        <v>9.336</v>
+        <v>7.794</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.96</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.0579</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.157</v>
+        <v>-1.737</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.93</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1109</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.327</v>
+        <v>-2.799</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.8</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2517</v>
+        <v>-0.2318</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.551</v>
+        <v>-6.954</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.46</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1112</v>
+        <v>1.1299</v>
       </c>
       <c r="J137" t="n">
-        <v>33.336</v>
+        <v>33.897</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.16</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4998</v>
+        <v>0.4577</v>
       </c>
       <c r="J138" t="n">
-        <v>14.994</v>
+        <v>13.731</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.85</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.4642</v>
+        <v>-0.4217</v>
       </c>
       <c r="J139" t="n">
-        <v>-13.926</v>
+        <v>-12.651</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.77</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.651</v>
+        <v>-0.6147</v>
       </c>
       <c r="J140" t="n">
-        <v>-19.53</v>
+        <v>-18.441</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.65</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.9102</v>
+        <v>-0.8952</v>
       </c>
       <c r="J141" t="n">
-        <v>-27.306</v>
+        <v>-26.856</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.29</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4542</v>
+        <v>0.4578</v>
       </c>
       <c r="J142" t="n">
-        <v>16.3512</v>
+        <v>16.4808</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.12</v>
       </c>
       <c r="I143" t="n">
-        <v>0.227</v>
+        <v>0.2111</v>
       </c>
       <c r="J143" t="n">
-        <v>8.172000000000001</v>
+        <v>7.5996</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.97</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.0586</v>
+        <v>-0.0459</v>
       </c>
       <c r="J144" t="n">
-        <v>-2.1096</v>
+        <v>-1.6524</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.92</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1241</v>
+        <v>-0.1055</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.4676</v>
+        <v>-3.798</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.73</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3204</v>
+        <v>-0.3037</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.5344</v>
+        <v>-10.9332</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.21</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3405</v>
+        <v>0.2815</v>
       </c>
       <c r="J147" t="n">
-        <v>12.258</v>
+        <v>10.134</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.11</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2065</v>
+        <v>0.1609</v>
       </c>
       <c r="J148" t="n">
-        <v>7.434</v>
+        <v>5.7924</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.93</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1092</v>
+        <v>-0.092</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.9312</v>
+        <v>-3.312</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.91</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1329</v>
+        <v>-0.1143</v>
       </c>
       <c r="J150" t="n">
-        <v>-4.7844</v>
+        <v>-4.1148</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3542</v>
+        <v>-0.3396</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.7512</v>
+        <v>-12.2256</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.31</v>
       </c>
       <c r="I152" t="n">
-        <v>0.7971</v>
+        <v>0.7703</v>
       </c>
       <c r="J152" t="n">
-        <v>23.1159</v>
+        <v>22.3387</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.22</v>
       </c>
       <c r="I153" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J153" t="n">
-        <v>17.5537</v>
+        <v>16.472</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.21</v>
       </c>
       <c r="I154" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.5451</v>
       </c>
       <c r="J154" t="n">
-        <v>16.9128</v>
+        <v>15.8079</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.01</v>
       </c>
       <c r="I155" t="n">
-        <v>0.044</v>
+        <v>0.0329</v>
       </c>
       <c r="J155" t="n">
-        <v>1.276</v>
+        <v>0.9540999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.75</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7201</v>
+        <v>-0.6902</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.8829</v>
+        <v>-20.0158</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.27</v>
       </c>
       <c r="I157" t="n">
-        <v>0.5849</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J157" t="n">
-        <v>16.9621</v>
+        <v>15.3903</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.0774</v>
       </c>
       <c r="J158" t="n">
-        <v>-2.6477</v>
+        <v>-2.2446</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.83</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.212</v>
+        <v>-0.1924</v>
       </c>
       <c r="J159" t="n">
-        <v>-6.148</v>
+        <v>-5.5796</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2904</v>
+        <v>-0.2719</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.4216</v>
+        <v>-7.8851</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.66</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3738</v>
+        <v>-0.3603</v>
       </c>
       <c r="J161" t="n">
-        <v>-10.8402</v>
+        <v>-10.4487</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.8186</v>
+        <v>0.794</v>
       </c>
       <c r="J162" t="n">
-        <v>22.1022</v>
+        <v>21.438</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.19</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5548</v>
+        <v>0.5144</v>
       </c>
       <c r="J163" t="n">
-        <v>14.9796</v>
+        <v>13.8888</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.99</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.0634</v>
+        <v>-0.0456</v>
       </c>
       <c r="J164" t="n">
-        <v>-1.7118</v>
+        <v>-1.2312</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.88</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.4005</v>
+        <v>-0.3574</v>
       </c>
       <c r="J165" t="n">
-        <v>-10.8135</v>
+        <v>-9.649800000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6171</v>
+        <v>-0.5794</v>
       </c>
       <c r="J166" t="n">
-        <v>-16.6617</v>
+        <v>-15.6438</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.15</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3721</v>
+        <v>0.3186</v>
       </c>
       <c r="J167" t="n">
-        <v>10.0467</v>
+        <v>8.6022</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.02</v>
       </c>
       <c r="I168" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0658</v>
       </c>
       <c r="J168" t="n">
-        <v>2.4516</v>
+        <v>1.7766</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0508</v>
+        <v>-0.0409</v>
       </c>
       <c r="J169" t="n">
-        <v>-1.3716</v>
+        <v>-1.1043</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.89</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.15</v>
+        <v>-0.132</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.05</v>
+        <v>-3.564</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.46</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5488</v>
+        <v>-0.5562</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.8176</v>
+        <v>-15.0174</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>0.0141</v>
+        <v>0.0097</v>
       </c>
       <c r="J172" t="n">
-        <v>0.3807</v>
+        <v>0.2619</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>0.0141</v>
+        <v>0.0097</v>
       </c>
       <c r="J173" t="n">
-        <v>0.3807</v>
+        <v>0.2619</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.0926</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.5002</v>
+        <v>-2.1141</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.85</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1928</v>
+        <v>-0.1732</v>
       </c>
       <c r="J175" t="n">
-        <v>-5.2056</v>
+        <v>-4.6764</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.73</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3107</v>
+        <v>-0.2931</v>
       </c>
       <c r="J176" t="n">
-        <v>-8.3889</v>
+        <v>-7.9137</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.31</v>
       </c>
       <c r="I177" t="n">
-        <v>0.8179</v>
+        <v>0.7932</v>
       </c>
       <c r="J177" t="n">
-        <v>22.0833</v>
+        <v>21.4164</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.01</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0549</v>
+        <v>0.0409</v>
       </c>
       <c r="J178" t="n">
-        <v>1.4823</v>
+        <v>1.1043</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.0044</v>
+        <v>-0.0024</v>
       </c>
       <c r="J179" t="n">
-        <v>-0.1188</v>
+        <v>-0.0648</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2368</v>
+        <v>-0.1989</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.3936</v>
+        <v>-5.3703</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.91</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3219</v>
+        <v>-0.2801</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.6913</v>
+        <v>-7.5627</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.13</v>
       </c>
       <c r="I182" t="n">
-        <v>0.3108</v>
+        <v>0.2594</v>
       </c>
       <c r="J182" t="n">
-        <v>12.432</v>
+        <v>10.376</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.05</v>
       </c>
       <c r="I183" t="n">
-        <v>0.1488</v>
+        <v>0.1145</v>
       </c>
       <c r="J183" t="n">
-        <v>5.952</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0423</v>
+        <v>-0.0322</v>
       </c>
       <c r="J184" t="n">
-        <v>-1.692</v>
+        <v>-1.288</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.93</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.111</v>
+        <v>-0.0934</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.44</v>
+        <v>-3.736</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.88</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.1688</v>
+        <v>-0.1485</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.752</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.35</v>
       </c>
       <c r="I187" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.8862</v>
       </c>
       <c r="J187" t="n">
-        <v>36.108</v>
+        <v>35.448</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.28</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.7257</v>
       </c>
       <c r="J188" t="n">
-        <v>30.22</v>
+        <v>29.028</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.21</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6012</v>
+        <v>0.5624</v>
       </c>
       <c r="J189" t="n">
-        <v>24.048</v>
+        <v>22.496</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.4994</v>
+        <v>-0.4572</v>
       </c>
       <c r="J190" t="n">
-        <v>-19.976</v>
+        <v>-18.288</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.47</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.2801</v>
+        <v>-1.3188</v>
       </c>
       <c r="J191" t="n">
-        <v>-51.204</v>
+        <v>-52.752</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.27</v>
       </c>
       <c r="I192" t="n">
-        <v>0.7359</v>
+        <v>0.7048</v>
       </c>
       <c r="J192" t="n">
-        <v>21.3411</v>
+        <v>20.4392</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.25</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6923</v>
+        <v>0.6582</v>
       </c>
       <c r="J193" t="n">
-        <v>20.0767</v>
+        <v>19.0878</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.14</v>
       </c>
       <c r="I194" t="n">
-        <v>0.438</v>
+        <v>0.3955</v>
       </c>
       <c r="J194" t="n">
-        <v>12.702</v>
+        <v>11.4695</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.95</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2046</v>
+        <v>-0.1692</v>
       </c>
       <c r="J195" t="n">
-        <v>-5.9334</v>
+        <v>-4.9068</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.51</v>
       </c>
       <c r="I196" t="n">
-        <v>-1.2013</v>
+        <v>-1.2268</v>
       </c>
       <c r="J196" t="n">
-        <v>-34.8377</v>
+        <v>-35.5772</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.21</v>
       </c>
       <c r="I197" t="n">
-        <v>0.4588</v>
+        <v>0.401</v>
       </c>
       <c r="J197" t="n">
-        <v>13.3052</v>
+        <v>11.629</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.06</v>
       </c>
       <c r="I198" t="n">
-        <v>0.1755</v>
+        <v>0.1371</v>
       </c>
       <c r="J198" t="n">
-        <v>5.0895</v>
+        <v>3.9759</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0838</v>
+        <v>-0.0689</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.4302</v>
+        <v>-1.9981</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.91</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1328</v>
+        <v>-0.1141</v>
       </c>
       <c r="J200" t="n">
-        <v>-3.8512</v>
+        <v>-3.3089</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.71</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3355</v>
+        <v>-0.3196</v>
       </c>
       <c r="J201" t="n">
-        <v>-9.7295</v>
+        <v>-9.2684</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.99</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0246</v>
+        <v>0.0381</v>
       </c>
       <c r="J202" t="n">
-        <v>0.5658</v>
+        <v>0.8763</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.273</v>
+        <v>-0.2586</v>
       </c>
       <c r="J203" t="n">
-        <v>-6.279</v>
+        <v>-5.9478</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.63</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3801</v>
+        <v>-0.368</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.7423</v>
+        <v>-8.464</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.61</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.3979</v>
+        <v>-0.3868</v>
       </c>
       <c r="J205" t="n">
-        <v>-9.1517</v>
+        <v>-8.8964</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4423</v>
+        <v>-0.4345</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.1729</v>
+        <v>-9.993499999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.55</v>
       </c>
       <c r="I207" t="n">
-        <v>0.665</v>
+        <v>0.593</v>
       </c>
       <c r="J207" t="n">
-        <v>15.295</v>
+        <v>13.639</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.51</v>
       </c>
       <c r="I208" t="n">
-        <v>0.6252</v>
+        <v>0.5538</v>
       </c>
       <c r="J208" t="n">
-        <v>14.3796</v>
+        <v>12.7374</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.2</v>
       </c>
       <c r="I209" t="n">
-        <v>0.2947</v>
+        <v>0.2443</v>
       </c>
       <c r="J209" t="n">
-        <v>6.7781</v>
+        <v>5.6189</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.14</v>
       </c>
       <c r="I210" t="n">
-        <v>0.2191</v>
+        <v>0.1771</v>
       </c>
       <c r="J210" t="n">
-        <v>5.0393</v>
+        <v>4.0733</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1201</v>
+        <v>-0.1029</v>
       </c>
       <c r="J211" t="n">
-        <v>-2.7623</v>
+        <v>-2.3667</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.2</v>
       </c>
       <c r="I212" t="n">
-        <v>0.5843</v>
+        <v>0.5448</v>
       </c>
       <c r="J212" t="n">
-        <v>16.3604</v>
+        <v>15.2544</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.09</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3128</v>
+        <v>0.2721</v>
       </c>
       <c r="J213" t="n">
-        <v>8.7584</v>
+        <v>7.6188</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.137</v>
+        <v>-0.1087</v>
       </c>
       <c r="J214" t="n">
-        <v>-3.836</v>
+        <v>-3.0436</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.2323</v>
+        <v>-0.1952</v>
       </c>
       <c r="J215" t="n">
-        <v>-6.5044</v>
+        <v>-5.4656</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.85</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.471</v>
+        <v>-0.4283</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.188</v>
+        <v>-11.9924</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.06</v>
       </c>
       <c r="I217" t="n">
-        <v>0.184</v>
+        <v>0.1444</v>
       </c>
       <c r="J217" t="n">
-        <v>5.152</v>
+        <v>4.0432</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.04</v>
       </c>
       <c r="I218" t="n">
-        <v>0.1374</v>
+        <v>0.1041</v>
       </c>
       <c r="J218" t="n">
-        <v>3.8472</v>
+        <v>2.9148</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.97</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0535</v>
+        <v>-0.043</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.498</v>
+        <v>-1.204</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.93</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.1065</v>
+        <v>-0.0905</v>
       </c>
       <c r="J220" t="n">
-        <v>-2.982</v>
+        <v>-2.534</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.63</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4042</v>
+        <v>-0.3937</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.3176</v>
+        <v>-11.0236</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.29</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5885</v>
+        <v>0.5301</v>
       </c>
       <c r="J222" t="n">
-        <v>16.478</v>
+        <v>14.8428</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.17</v>
       </c>
       <c r="I223" t="n">
-        <v>0.3873</v>
+        <v>0.3316</v>
       </c>
       <c r="J223" t="n">
-        <v>10.8444</v>
+        <v>9.284800000000001</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.95</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0843</v>
+        <v>-0.0692</v>
       </c>
       <c r="J224" t="n">
-        <v>-2.3604</v>
+        <v>-1.9376</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.92</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1217</v>
+        <v>-0.1036</v>
       </c>
       <c r="J225" t="n">
-        <v>-3.4076</v>
+        <v>-2.9008</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.55</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4786</v>
+        <v>-0.4771</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.4008</v>
+        <v>-13.3588</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.43</v>
       </c>
       <c r="I227" t="n">
-        <v>1.0334</v>
+        <v>1.0373</v>
       </c>
       <c r="J227" t="n">
-        <v>28.9352</v>
+        <v>29.0444</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.29</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7623</v>
+        <v>0.7328</v>
       </c>
       <c r="J228" t="n">
-        <v>21.3444</v>
+        <v>20.5184</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.97</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.1489</v>
+        <v>-0.1181</v>
       </c>
       <c r="J229" t="n">
-        <v>-4.1692</v>
+        <v>-3.3068</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.91</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3301</v>
+        <v>-0.288</v>
       </c>
       <c r="J230" t="n">
-        <v>-9.242800000000001</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6486</v>
+        <v>-0.6133</v>
       </c>
       <c r="J231" t="n">
-        <v>-18.1608</v>
+        <v>-17.1724</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>0.96</v>
       </c>
       <c r="I232" t="n">
-        <v>-0.0389</v>
+        <v>-0.0266</v>
       </c>
       <c r="J232" t="n">
-        <v>-0.8947000000000001</v>
+        <v>-0.6118</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>0.9</v>
       </c>
       <c r="I233" t="n">
-        <v>-0.1182</v>
+        <v>-0.103</v>
       </c>
       <c r="J233" t="n">
-        <v>-2.7186</v>
+        <v>-2.369</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>0.76</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.2665</v>
+        <v>-0.2512</v>
       </c>
       <c r="J234" t="n">
-        <v>-6.1295</v>
+        <v>-5.7776</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.62</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.3923</v>
+        <v>-0.3805</v>
       </c>
       <c r="J235" t="n">
-        <v>-9.0229</v>
+        <v>-8.7515</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.43</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5589</v>
+        <v>-0.5656</v>
       </c>
       <c r="J236" t="n">
-        <v>-12.8547</v>
+        <v>-13.0088</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.7</v>
       </c>
       <c r="I237" t="n">
-        <v>1.3632</v>
+        <v>1.3871</v>
       </c>
       <c r="J237" t="n">
-        <v>31.3536</v>
+        <v>31.9033</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.35</v>
       </c>
       <c r="I238" t="n">
-        <v>0.8465</v>
+        <v>0.8264</v>
       </c>
       <c r="J238" t="n">
-        <v>19.4695</v>
+        <v>19.0072</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.18</v>
       </c>
       <c r="I239" t="n">
-        <v>0.4981</v>
+        <v>0.465</v>
       </c>
       <c r="J239" t="n">
-        <v>11.4563</v>
+        <v>10.695</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>1.15</v>
       </c>
       <c r="I240" t="n">
-        <v>0.4292</v>
+        <v>0.3957</v>
       </c>
       <c r="J240" t="n">
-        <v>9.871600000000001</v>
+        <v>9.101100000000001</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.77</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.698</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-16.054</v>
+        <v>-15.4077</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.56</v>
       </c>
       <c r="I242" t="n">
-        <v>1.1712</v>
+        <v>1.1851</v>
       </c>
       <c r="J242" t="n">
-        <v>26.9376</v>
+        <v>27.2573</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.43</v>
       </c>
       <c r="I243" t="n">
-        <v>0.987</v>
+        <v>0.9832</v>
       </c>
       <c r="J243" t="n">
-        <v>22.701</v>
+        <v>22.6136</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.4</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9345</v>
+        <v>0.9232</v>
       </c>
       <c r="J244" t="n">
-        <v>21.4935</v>
+        <v>21.2336</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.22</v>
       </c>
       <c r="I245" t="n">
-        <v>0.5804</v>
+        <v>0.5503</v>
       </c>
       <c r="J245" t="n">
-        <v>13.3492</v>
+        <v>12.6569</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.73</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.7913</v>
+        <v>-0.7721</v>
       </c>
       <c r="J246" t="n">
-        <v>-18.1999</v>
+        <v>-17.7583</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.95</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0483</v>
+        <v>-0.0342</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.1109</v>
+        <v>-0.7866</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.84</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.1823</v>
+        <v>-0.1668</v>
       </c>
       <c r="J248" t="n">
-        <v>-4.1929</v>
+        <v>-3.8364</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.8</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2244</v>
+        <v>-0.2093</v>
       </c>
       <c r="J249" t="n">
-        <v>-5.1612</v>
+        <v>-4.8139</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.52</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.478</v>
+        <v>-0.4738</v>
       </c>
       <c r="J250" t="n">
-        <v>-10.994</v>
+        <v>-10.8974</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.45</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.5391</v>
+        <v>-0.5426</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.3993</v>
+        <v>-12.4798</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.58</v>
       </c>
       <c r="I252" t="n">
-        <v>1.2674</v>
+        <v>1.2936</v>
       </c>
       <c r="J252" t="n">
-        <v>51.9634</v>
+        <v>53.0376</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.0026</v>
+        <v>-0.0012</v>
       </c>
       <c r="J253" t="n">
-        <v>-0.1066</v>
+        <v>-0.0492</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.98</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1028</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.2148</v>
+        <v>-3.2267</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.93</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2637</v>
+        <v>-0.2245</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.8117</v>
+        <v>-9.204499999999999</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.62</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.9808</v>
+        <v>-0.9751</v>
       </c>
       <c r="J256" t="n">
-        <v>-40.2128</v>
+        <v>-39.9791</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.29</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6046</v>
+        <v>0.5488</v>
       </c>
       <c r="J257" t="n">
-        <v>24.7886</v>
+        <v>22.5008</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.09</v>
       </c>
       <c r="I258" t="n">
-        <v>0.248</v>
+        <v>0.2017</v>
       </c>
       <c r="J258" t="n">
-        <v>10.168</v>
+        <v>8.2697</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.89</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.152</v>
+        <v>-0.1332</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.232</v>
+        <v>-5.4612</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.71</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3315</v>
+        <v>-0.3152</v>
       </c>
       <c r="J260" t="n">
-        <v>-13.5915</v>
+        <v>-12.9232</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.65</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.3863</v>
+        <v>-0.3741</v>
       </c>
       <c r="J261" t="n">
-        <v>-15.8383</v>
+        <v>-15.3381</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.15</v>
       </c>
       <c r="I262" t="n">
-        <v>0.3947</v>
+        <v>0.3442</v>
       </c>
       <c r="J262" t="n">
-        <v>9.472799999999999</v>
+        <v>8.2608</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.06</v>
       </c>
       <c r="I263" t="n">
-        <v>0.2095</v>
+        <v>0.1699</v>
       </c>
       <c r="J263" t="n">
-        <v>5.028</v>
+        <v>4.0776</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>0.87</v>
       </c>
       <c r="I264" t="n">
-        <v>-0.1668</v>
+        <v>-0.1499</v>
       </c>
       <c r="J264" t="n">
-        <v>-4.0032</v>
+        <v>-3.5976</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>0.6</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.4214</v>
+        <v>-0.4119</v>
       </c>
       <c r="J265" t="n">
-        <v>-10.1136</v>
+        <v>-9.8856</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.48</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.526</v>
+        <v>-0.5291</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.624</v>
+        <v>-12.6984</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.53</v>
       </c>
       <c r="I267" t="n">
-        <v>1.1741</v>
+        <v>1.1905</v>
       </c>
       <c r="J267" t="n">
-        <v>28.1784</v>
+        <v>28.572</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.05</v>
       </c>
       <c r="I268" t="n">
-        <v>0.1879</v>
+        <v>0.1586</v>
       </c>
       <c r="J268" t="n">
-        <v>4.5096</v>
+        <v>3.8064</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.0139</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="J269" t="n">
-        <v>-0.3336</v>
+        <v>-0.2304</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.98</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.1149</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="J270" t="n">
-        <v>-2.7576</v>
+        <v>-2.1216</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.89</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.3862</v>
+        <v>-0.3433</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.268800000000001</v>
+        <v>-8.2392</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.32</v>
       </c>
       <c r="I272" t="n">
-        <v>0.6544</v>
+        <v>0.6004</v>
       </c>
       <c r="J272" t="n">
-        <v>18.9776</v>
+        <v>17.4116</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>0.0106</v>
+        <v>0.0068</v>
       </c>
       <c r="J273" t="n">
-        <v>0.3074</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.88</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.1626</v>
+        <v>-0.1435</v>
       </c>
       <c r="J274" t="n">
-        <v>-4.7154</v>
+        <v>-4.1615</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.72</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3218</v>
+        <v>-0.3049</v>
       </c>
       <c r="J275" t="n">
-        <v>-9.3322</v>
+        <v>-8.8421</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3496</v>
+        <v>-0.3344</v>
       </c>
       <c r="J276" t="n">
-        <v>-10.1384</v>
+        <v>-9.6976</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.25</v>
       </c>
       <c r="I277" t="n">
-        <v>0.6929</v>
+        <v>0.659</v>
       </c>
       <c r="J277" t="n">
-        <v>20.0941</v>
+        <v>19.111</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.07</v>
       </c>
       <c r="I278" t="n">
-        <v>0.255</v>
+        <v>0.2176</v>
       </c>
       <c r="J278" t="n">
-        <v>7.395</v>
+        <v>6.3104</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.0026</v>
+        <v>-0.0012</v>
       </c>
       <c r="J279" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0348</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2345</v>
+        <v>-0.197</v>
       </c>
       <c r="J280" t="n">
-        <v>-6.8005</v>
+        <v>-5.713</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.85</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.4734</v>
+        <v>-0.4308</v>
       </c>
       <c r="J281" t="n">
-        <v>-13.7286</v>
+        <v>-12.4932</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.49</v>
       </c>
       <c r="I282" t="n">
-        <v>0.9437</v>
+        <v>0.9191</v>
       </c>
       <c r="J282" t="n">
-        <v>24.5362</v>
+        <v>23.8966</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.91</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1253</v>
+        <v>-0.1095</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.2578</v>
+        <v>-2.847</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.8</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2395</v>
+        <v>-0.2203</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.227</v>
+        <v>-5.7278</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.68</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3529</v>
+        <v>-0.3378</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.1754</v>
+        <v>-8.7828</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.44</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5629</v>
+        <v>-0.572</v>
       </c>
       <c r="J286" t="n">
-        <v>-14.6354</v>
+        <v>-14.872</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.51</v>
       </c>
       <c r="I287" t="n">
-        <v>1.1277</v>
+        <v>1.1404</v>
       </c>
       <c r="J287" t="n">
-        <v>29.3202</v>
+        <v>29.6504</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.4</v>
       </c>
       <c r="I288" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9489</v>
       </c>
       <c r="J288" t="n">
-        <v>24.9392</v>
+        <v>24.6714</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.15</v>
       </c>
       <c r="I289" t="n">
-        <v>0.4389</v>
+        <v>0.4021</v>
       </c>
       <c r="J289" t="n">
-        <v>11.4114</v>
+        <v>10.4546</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>0.91</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.3456</v>
+        <v>-0.3041</v>
       </c>
       <c r="J290" t="n">
-        <v>-8.9856</v>
+        <v>-7.9066</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.82</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.5717</v>
+        <v>-0.5339</v>
       </c>
       <c r="J291" t="n">
-        <v>-14.8642</v>
+        <v>-13.8814</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.13</v>
       </c>
       <c r="I292" t="n">
-        <v>0.4189</v>
+        <v>0.3852</v>
       </c>
       <c r="J292" t="n">
-        <v>9.6347</v>
+        <v>8.8596</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.7</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.3175</v>
+        <v>-0.3038</v>
       </c>
       <c r="J293" t="n">
-        <v>-7.3025</v>
+        <v>-6.9874</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.59</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.4147</v>
+        <v>-0.4048</v>
       </c>
       <c r="J294" t="n">
-        <v>-9.5381</v>
+        <v>-9.3104</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.58</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4235</v>
+        <v>-0.4143</v>
       </c>
       <c r="J295" t="n">
-        <v>-9.740500000000001</v>
+        <v>-9.5289</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.5</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.494</v>
+        <v>-0.4916</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.362</v>
+        <v>-11.3068</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.6</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2347</v>
+        <v>1.2512</v>
       </c>
       <c r="J297" t="n">
-        <v>28.3981</v>
+        <v>28.7776</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.59</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2214</v>
+        <v>1.2373</v>
       </c>
       <c r="J298" t="n">
-        <v>28.0922</v>
+        <v>28.4579</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.45</v>
       </c>
       <c r="I299" t="n">
-        <v>1.0285</v>
+        <v>1.0306</v>
       </c>
       <c r="J299" t="n">
-        <v>23.6555</v>
+        <v>23.7038</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.9</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.3836</v>
+        <v>-0.343</v>
       </c>
       <c r="J300" t="n">
-        <v>-8.822800000000001</v>
+        <v>-7.889</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.1318</v>
+        <v>-1.1527</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.0314</v>
+        <v>-26.5121</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>0.93</v>
       </c>
       <c r="I302" t="n">
-        <v>-0.0644</v>
+        <v>-0.0469</v>
       </c>
       <c r="J302" t="n">
-        <v>-1.4168</v>
+        <v>-1.0318</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I303" t="n">
-        <v>-0.2059</v>
+        <v>-0.1906</v>
       </c>
       <c r="J303" t="n">
-        <v>-4.5298</v>
+        <v>-4.1932</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>0.67</v>
       </c>
       <c r="I304" t="n">
-        <v>-0.3409</v>
+        <v>-0.3288</v>
       </c>
       <c r="J304" t="n">
-        <v>-7.4998</v>
+        <v>-7.2336</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>0.64</v>
       </c>
       <c r="I305" t="n">
-        <v>-0.3666</v>
+        <v>-0.355</v>
       </c>
       <c r="J305" t="n">
-        <v>-8.065200000000001</v>
+        <v>-7.81</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.29</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.6726</v>
+        <v>-0.6983</v>
       </c>
       <c r="J306" t="n">
-        <v>-14.7972</v>
+        <v>-15.3626</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.65</v>
       </c>
       <c r="I307" t="n">
-        <v>1.2739</v>
+        <v>1.292</v>
       </c>
       <c r="J307" t="n">
-        <v>28.0258</v>
+        <v>28.424</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.49</v>
       </c>
       <c r="I308" t="n">
-        <v>1.065</v>
+        <v>1.075</v>
       </c>
       <c r="J308" t="n">
-        <v>23.43</v>
+        <v>23.65</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>1.34</v>
       </c>
       <c r="I309" t="n">
-        <v>0.8114</v>
+        <v>0.7945</v>
       </c>
       <c r="J309" t="n">
-        <v>17.8508</v>
+        <v>17.479</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>1.28</v>
       </c>
       <c r="I310" t="n">
-        <v>0.6947</v>
+        <v>0.672</v>
       </c>
       <c r="J310" t="n">
-        <v>15.2834</v>
+        <v>14.784</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.96</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2292</v>
+        <v>-0.1977</v>
       </c>
       <c r="J311" t="n">
-        <v>-5.0424</v>
+        <v>-4.3494</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.23</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5285</v>
+        <v>0.4755</v>
       </c>
       <c r="J312" t="n">
-        <v>13.741</v>
+        <v>12.363</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>0.8</v>
       </c>
       <c r="I313" t="n">
-        <v>-0.2391</v>
+        <v>-0.22</v>
       </c>
       <c r="J313" t="n">
-        <v>-6.2166</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>0.8</v>
       </c>
       <c r="I314" t="n">
-        <v>-0.2391</v>
+        <v>-0.22</v>
       </c>
       <c r="J314" t="n">
-        <v>-6.2166</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>0.75</v>
       </c>
       <c r="I315" t="n">
-        <v>-0.2873</v>
+        <v>-0.269</v>
       </c>
       <c r="J315" t="n">
-        <v>-7.4698</v>
+        <v>-6.994</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.72</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.3155</v>
+        <v>-0.2983</v>
       </c>
       <c r="J316" t="n">
-        <v>-8.202999999999999</v>
+        <v>-7.7558</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.64</v>
       </c>
       <c r="I317" t="n">
-        <v>1.2937</v>
+        <v>1.3138</v>
       </c>
       <c r="J317" t="n">
-        <v>33.6362</v>
+        <v>34.1588</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.33</v>
       </c>
       <c r="I318" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7904</v>
       </c>
       <c r="J318" t="n">
-        <v>21.164</v>
+        <v>20.5504</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.25</v>
       </c>
       <c r="I319" t="n">
-        <v>0.651</v>
+        <v>0.6192</v>
       </c>
       <c r="J319" t="n">
-        <v>16.926</v>
+        <v>16.0992</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>1.17</v>
       </c>
       <c r="I320" t="n">
-        <v>0.4801</v>
+        <v>0.4452</v>
       </c>
       <c r="J320" t="n">
-        <v>12.4826</v>
+        <v>11.5752</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.59</v>
       </c>
       <c r="I321" t="n">
-        <v>-1.0694</v>
+        <v>-1.0806</v>
       </c>
       <c r="J321" t="n">
-        <v>-27.8044</v>
+        <v>-28.0956</v>
       </c>
     </row>
   </sheetData>
